--- a/Results/2-26-2026/Optimal Design Hardware Results/Optimal Design.xlsx
+++ b/Results/2-26-2026/Optimal Design Hardware Results/Optimal Design.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://djpropertycom-my.sharepoint.com/personal/noah_familiajones_org/Documents/Work and Projects/Github/Bio-Inspired-Sensing/Results/2-26-2026/Optimal Design Hardware Results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4159" documentId="8_{DFFD6B0C-681F-42C8-B2E4-5D4B90AAE966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4566641B-A51D-4D08-839F-F01A811DD151}"/>
+  <xr:revisionPtr revIDLastSave="4229" documentId="8_{DFFD6B0C-681F-42C8-B2E4-5D4B90AAE966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3745147F-DC5E-40EA-8FF7-64621C0B037A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3D16C37F-3C74-4527-A308-796C339DFE9F}"/>
   </bookViews>
@@ -18,6 +18,7 @@
     <sheet name="Distal Vali (one truth)" sheetId="41" r:id="rId3"/>
     <sheet name="Distal Vali (five truth)" sheetId="40" r:id="rId4"/>
     <sheet name="Conversion" sheetId="4" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="45" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -62,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="48">
   <si>
     <t>Fx (N)</t>
   </si>
@@ -192,6 +193,21 @@
   <si>
     <t>NRMSE (%FS)</t>
   </si>
+  <si>
+    <t>[</t>
+  </si>
+  <si>
+    <t>;</t>
+  </si>
+  <si>
+    <t>]</t>
+  </si>
+  <si>
+    <t>Overall NRMSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RMSE </t>
+  </si>
 </sst>
 </file>
 
@@ -242,7 +258,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -300,6 +316,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -477,7 +499,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -501,7 +523,10 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="3" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="3" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -516,15 +541,6 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -537,10 +553,13 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -552,6 +571,25 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Good" xfId="1" builtinId="26"/>
@@ -574,10 +612,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -897,7 +931,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B763EDC-8536-442D-A8D3-F37978D4DE80}">
-  <dimension ref="A1:DX62"/>
+  <dimension ref="A1:EE117"/>
   <sheetFormatPr defaultRowHeight="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="7.42578125" bestFit="1" customWidth="1"/>
@@ -914,61 +948,74 @@
     <col min="24" max="24" width="7.7109375" bestFit="1" customWidth="1"/>
     <col min="25" max="27" width="7.28515625" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="14" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="32" max="34" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:128" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+    <row r="1" spans="1:135" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="26" t="s">
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
-      <c r="O1" s="27"/>
-      <c r="P1" s="28" t="s">
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
+      <c r="P1" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="Q1" s="29"/>
-      <c r="R1" s="29"/>
-      <c r="S1" s="29"/>
-      <c r="T1" s="29"/>
-      <c r="U1" s="29"/>
-      <c r="V1" s="30" t="s">
+      <c r="Q1" s="35"/>
+      <c r="R1" s="35"/>
+      <c r="S1" s="35"/>
+      <c r="T1" s="35"/>
+      <c r="U1" s="35"/>
+      <c r="V1" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="W1" s="30"/>
-      <c r="X1" s="30"/>
-      <c r="Y1" s="30"/>
-      <c r="Z1" s="30"/>
-      <c r="AA1" s="30"/>
-      <c r="AB1" s="30"/>
-      <c r="AC1" s="23" t="s">
+      <c r="W1" s="40"/>
+      <c r="X1" s="40"/>
+      <c r="Y1" s="40"/>
+      <c r="Z1" s="40"/>
+      <c r="AA1" s="41"/>
+      <c r="AB1" s="42" t="s">
+        <v>47</v>
+      </c>
+      <c r="AC1" s="43"/>
+      <c r="AD1" s="43"/>
+      <c r="AE1" s="43"/>
+      <c r="AF1" s="43"/>
+      <c r="AG1" s="43"/>
+      <c r="AH1" s="43"/>
+      <c r="AI1" s="44"/>
+      <c r="AJ1" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="AD1" s="23"/>
-      <c r="AE1" s="23" t="s">
+      <c r="AK1" s="33"/>
+      <c r="AL1" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="AF1" s="23"/>
-      <c r="AG1" s="23"/>
-      <c r="AH1" s="23"/>
-      <c r="AI1" s="23"/>
-      <c r="AJ1" s="23"/>
+      <c r="AM1" s="33"/>
+      <c r="AN1" s="33"/>
+      <c r="AO1" s="33"/>
+      <c r="AP1" s="33"/>
+      <c r="AQ1" s="33"/>
     </row>
-    <row r="2" spans="1:128" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:135" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>22</v>
       </c>
@@ -1054,31 +1101,52 @@
         <v>42</v>
       </c>
       <c r="AC2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AG2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AI2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AJ2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AD2" s="6" t="s">
+      <c r="AK2" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="AE2" s="1" t="s">
+      <c r="AL2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="AF2" s="1" t="s">
+      <c r="AM2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="AG2" s="1" t="s">
+      <c r="AN2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AH2" s="1" t="s">
+      <c r="AO2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="AI2" s="1" t="s">
+      <c r="AP2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="AJ2" s="1" t="s">
+      <c r="AQ2" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:128" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:135" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="17">
         <v>0.57634630980000001</v>
       </c>
@@ -1167,41 +1235,62 @@
         <v>-0.33057668372159349</v>
       </c>
       <c r="AB3" s="16" cm="1">
-        <f t="array" ref="AB3">SQRT(SUMPRODUCT(((J3:O3-P3:U3)/$AE$3:$AJ$3)^2)/6)*100</f>
+        <f t="array" ref="AB3">SQRT(SUMPRODUCT(((J3:O3-P3:U3)/$AL$3:$AQ$3)^2)/6)*100</f>
         <v>1.1223523003448495</v>
       </c>
-      <c r="AC3" s="5">
+      <c r="AC3" s="5" cm="1">
+        <f t="array" ref="AC3">SQRT(SUMPRODUCT((J3:J52-P3:P52)^2)/50)</f>
+        <v>4.2957898131744708E-3</v>
+      </c>
+      <c r="AD3" s="5" cm="1">
+        <f t="array" ref="AD3">SQRT(SUMPRODUCT((K3:K52-Q3:Q52)^2)/50)</f>
+        <v>1.1340333669401691E-2</v>
+      </c>
+      <c r="AE3" s="5" cm="1">
+        <f t="array" ref="AE3">SQRT(SUMPRODUCT((L3:L52-R3:R52)^2)/50)</f>
+        <v>1.2305603576609031E-2</v>
+      </c>
+      <c r="AF3" s="5" cm="1">
+        <f t="array" ref="AF3">SQRT(SUMPRODUCT((M3:M52-S3:S52)^2)/50)</f>
+        <v>6.2312000600724671E-2</v>
+      </c>
+      <c r="AG3" s="5" cm="1">
+        <f t="array" ref="AG3">SQRT(SUMPRODUCT((N3:N52-T3:T52)^2)/50)</f>
+        <v>0.13663074284105178</v>
+      </c>
+      <c r="AH3" s="5" cm="1">
+        <f t="array" ref="AH3">SQRT(SUMPRODUCT((O3:O52-U3:U52)^2)/50)</f>
+        <v>0.1020552684785178</v>
+      </c>
+      <c r="AI3" s="16" cm="1">
+        <f t="array" ref="AI3">SQRT(SUMPRODUCT(((J3:O52-P3:U52)/$AL$3:$AQ$3)^2)/(50*6))*100</f>
+        <v>0.78768807598146806</v>
+      </c>
+      <c r="AJ3" s="5">
         <f>ABS(B3-E3)</f>
         <v>0.18000000000000002</v>
       </c>
-      <c r="AD3" s="13">
+      <c r="AK3" s="13">
         <v>63364.800162808497</v>
       </c>
-      <c r="AE3" s="19">
+      <c r="AL3" s="19">
         <v>1</v>
       </c>
-      <c r="AF3" s="19">
+      <c r="AM3" s="19">
         <v>1</v>
       </c>
-      <c r="AG3" s="19">
+      <c r="AN3" s="19">
         <v>1</v>
       </c>
-      <c r="AH3" s="19">
+      <c r="AO3" s="19">
         <v>60</v>
       </c>
-      <c r="AI3" s="19">
+      <c r="AP3" s="19">
         <v>20</v>
       </c>
-      <c r="AJ3" s="19">
+      <c r="AQ3" s="19">
         <v>20</v>
       </c>
-      <c r="AK3" s="15"/>
-      <c r="AL3" s="15"/>
-      <c r="AM3" s="15"/>
-      <c r="AN3" s="15"/>
-      <c r="AO3" s="15"/>
-      <c r="AP3" s="15"/>
-      <c r="AQ3" s="15"/>
       <c r="AR3" s="15"/>
       <c r="AS3" s="15"/>
       <c r="AT3" s="15"/>
@@ -1287,8 +1376,15 @@
       <c r="DV3" s="15"/>
       <c r="DW3" s="15"/>
       <c r="DX3" s="15"/>
+      <c r="DY3" s="15"/>
+      <c r="DZ3" s="15"/>
+      <c r="EA3" s="15"/>
+      <c r="EB3" s="15"/>
+      <c r="EC3" s="15"/>
+      <c r="ED3" s="15"/>
+      <c r="EE3" s="15"/>
     </row>
-    <row r="4" spans="1:128" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:135" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="17">
         <v>1.2961945501000001</v>
       </c>
@@ -1377,23 +1473,23 @@
         <v>0.1078645641653585</v>
       </c>
       <c r="AB4" s="16" cm="1">
-        <f t="array" ref="AB4">SQRT(SUMPRODUCT(((J4:O4-P4:U4)/$AE$3:$AJ$3)^2)/6)*100</f>
+        <f t="array" ref="AB4">SQRT(SUMPRODUCT(((J4:O4-P4:U4)/$AL$3:$AQ$3)^2)/6)*100</f>
         <v>0.56449983152991945</v>
       </c>
-      <c r="AC4" s="5">
-        <f t="shared" ref="AC4:AC52" si="7">ABS(B4-E4)</f>
+      <c r="AC4" s="16"/>
+      <c r="AD4" s="16"/>
+      <c r="AE4" s="16"/>
+      <c r="AF4" s="16"/>
+      <c r="AG4" s="16"/>
+      <c r="AH4" s="16"/>
+      <c r="AI4" s="16"/>
+      <c r="AJ4" s="5">
+        <f t="shared" ref="AJ4:AJ52" si="7">ABS(B4-E4)</f>
         <v>0.18000000000000002</v>
       </c>
-      <c r="AD4" s="13">
+      <c r="AK4" s="13">
         <v>330.78885343832201</v>
       </c>
-      <c r="AE4" s="15"/>
-      <c r="AF4" s="15"/>
-      <c r="AG4" s="15"/>
-      <c r="AH4" s="15"/>
-      <c r="AI4" s="15"/>
-      <c r="AJ4" s="15"/>
-      <c r="AK4" s="15"/>
       <c r="AL4" s="15"/>
       <c r="AM4" s="15"/>
       <c r="AN4" s="15"/>
@@ -1485,8 +1581,15 @@
       <c r="DV4" s="15"/>
       <c r="DW4" s="15"/>
       <c r="DX4" s="15"/>
+      <c r="DY4" s="15"/>
+      <c r="DZ4" s="15"/>
+      <c r="EA4" s="15"/>
+      <c r="EB4" s="15"/>
+      <c r="EC4" s="15"/>
+      <c r="ED4" s="15"/>
+      <c r="EE4" s="15"/>
     </row>
-    <row r="5" spans="1:128" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:135" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="17">
         <v>0.3432844504</v>
       </c>
@@ -1575,23 +1678,23 @@
         <v>5.098594268298718E-3</v>
       </c>
       <c r="AB5" s="16" cm="1">
-        <f t="array" ref="AB5">SQRT(SUMPRODUCT(((J5:O5-P5:U5)/$AE$3:$AJ$3)^2)/6)*100</f>
+        <f t="array" ref="AB5">SQRT(SUMPRODUCT(((J5:O5-P5:U5)/$AL$3:$AQ$3)^2)/6)*100</f>
         <v>0.36255561838979583</v>
       </c>
-      <c r="AC5" s="5">
+      <c r="AC5" s="16"/>
+      <c r="AD5" s="16"/>
+      <c r="AE5" s="16"/>
+      <c r="AF5" s="16"/>
+      <c r="AG5" s="16"/>
+      <c r="AH5" s="16"/>
+      <c r="AI5" s="16"/>
+      <c r="AJ5" s="5">
         <f t="shared" si="7"/>
         <v>0.18000000000000002</v>
       </c>
-      <c r="AD5" s="13">
+      <c r="AK5" s="13">
         <v>883.99451977233605</v>
       </c>
-      <c r="AE5" s="15"/>
-      <c r="AF5" s="15"/>
-      <c r="AG5" s="15"/>
-      <c r="AH5" s="15"/>
-      <c r="AI5" s="15"/>
-      <c r="AJ5" s="15"/>
-      <c r="AK5" s="15"/>
       <c r="AL5" s="15"/>
       <c r="AM5" s="15"/>
       <c r="AN5" s="15"/>
@@ -1683,8 +1786,15 @@
       <c r="DV5" s="15"/>
       <c r="DW5" s="15"/>
       <c r="DX5" s="15"/>
+      <c r="DY5" s="15"/>
+      <c r="DZ5" s="15"/>
+      <c r="EA5" s="15"/>
+      <c r="EB5" s="15"/>
+      <c r="EC5" s="15"/>
+      <c r="ED5" s="15"/>
+      <c r="EE5" s="15"/>
     </row>
-    <row r="6" spans="1:128" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:135" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="17">
         <v>0.83277602429999997</v>
       </c>
@@ -1773,23 +1883,23 @@
         <v>-5.5781336073658538E-2</v>
       </c>
       <c r="AB6" s="16" cm="1">
-        <f t="array" ref="AB6">SQRT(SUMPRODUCT(((J6:O6-P6:U6)/$AE$3:$AJ$3)^2)/6)*100</f>
+        <f t="array" ref="AB6">SQRT(SUMPRODUCT(((J6:O6-P6:U6)/$AL$3:$AQ$3)^2)/6)*100</f>
         <v>0.51301758759947491</v>
       </c>
-      <c r="AC6" s="5">
+      <c r="AC6" s="16"/>
+      <c r="AD6" s="16"/>
+      <c r="AE6" s="16"/>
+      <c r="AF6" s="16"/>
+      <c r="AG6" s="16"/>
+      <c r="AH6" s="16"/>
+      <c r="AI6" s="16"/>
+      <c r="AJ6" s="5">
         <f t="shared" si="7"/>
         <v>0.16</v>
       </c>
-      <c r="AD6" s="13">
+      <c r="AK6" s="13">
         <v>214.863490368529</v>
       </c>
-      <c r="AE6" s="15"/>
-      <c r="AF6" s="15"/>
-      <c r="AG6" s="15"/>
-      <c r="AH6" s="15"/>
-      <c r="AI6" s="15"/>
-      <c r="AJ6" s="15"/>
-      <c r="AK6" s="15"/>
       <c r="AL6" s="15"/>
       <c r="AM6" s="15"/>
       <c r="AN6" s="15"/>
@@ -1881,8 +1991,15 @@
       <c r="DV6" s="15"/>
       <c r="DW6" s="15"/>
       <c r="DX6" s="15"/>
+      <c r="DY6" s="15"/>
+      <c r="DZ6" s="15"/>
+      <c r="EA6" s="15"/>
+      <c r="EB6" s="15"/>
+      <c r="EC6" s="15"/>
+      <c r="ED6" s="15"/>
+      <c r="EE6" s="15"/>
     </row>
-    <row r="7" spans="1:128" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:135" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="17">
         <v>0.3898403909</v>
       </c>
@@ -1971,23 +2088,23 @@
         <v>-0.15307237416613695</v>
       </c>
       <c r="AB7" s="16" cm="1">
-        <f t="array" ref="AB7">SQRT(SUMPRODUCT(((J7:O7-P7:U7)/$AE$3:$AJ$3)^2)/6)*100</f>
+        <f t="array" ref="AB7">SQRT(SUMPRODUCT(((J7:O7-P7:U7)/$AL$3:$AQ$3)^2)/6)*100</f>
         <v>0.35239692263204508</v>
       </c>
-      <c r="AC7" s="5">
+      <c r="AC7" s="16"/>
+      <c r="AD7" s="16"/>
+      <c r="AE7" s="16"/>
+      <c r="AF7" s="16"/>
+      <c r="AG7" s="16"/>
+      <c r="AH7" s="16"/>
+      <c r="AI7" s="16"/>
+      <c r="AJ7" s="5">
         <f t="shared" si="7"/>
         <v>0.16</v>
       </c>
-      <c r="AD7" s="13">
+      <c r="AK7" s="13">
         <v>1314.4733005805001</v>
       </c>
-      <c r="AE7" s="15"/>
-      <c r="AF7" s="15"/>
-      <c r="AG7" s="15"/>
-      <c r="AH7" s="15"/>
-      <c r="AI7" s="15"/>
-      <c r="AJ7" s="15"/>
-      <c r="AK7" s="15"/>
       <c r="AL7" s="15"/>
       <c r="AM7" s="15"/>
       <c r="AN7" s="15"/>
@@ -2079,8 +2196,15 @@
       <c r="DV7" s="15"/>
       <c r="DW7" s="15"/>
       <c r="DX7" s="15"/>
+      <c r="DY7" s="15"/>
+      <c r="DZ7" s="15"/>
+      <c r="EA7" s="15"/>
+      <c r="EB7" s="15"/>
+      <c r="EC7" s="15"/>
+      <c r="ED7" s="15"/>
+      <c r="EE7" s="15"/>
     </row>
-    <row r="8" spans="1:128" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:135" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="17">
         <v>0.86958752539999995</v>
       </c>
@@ -2169,23 +2293,23 @@
         <v>-7.1179441039073033E-2</v>
       </c>
       <c r="AB8" s="16" cm="1">
-        <f t="array" ref="AB8">SQRT(SUMPRODUCT(((J8:O8-P8:U8)/$AE$3:$AJ$3)^2)/6)*100</f>
+        <f t="array" ref="AB8">SQRT(SUMPRODUCT(((J8:O8-P8:U8)/$AL$3:$AQ$3)^2)/6)*100</f>
         <v>0.62991033434261634</v>
       </c>
-      <c r="AC8" s="5">
+      <c r="AC8" s="16"/>
+      <c r="AD8" s="16"/>
+      <c r="AE8" s="16"/>
+      <c r="AF8" s="16"/>
+      <c r="AG8" s="16"/>
+      <c r="AH8" s="16"/>
+      <c r="AI8" s="16"/>
+      <c r="AJ8" s="5">
         <f t="shared" si="7"/>
         <v>0.16</v>
       </c>
-      <c r="AD8" s="13">
+      <c r="AK8" s="13">
         <v>494.45546440875</v>
       </c>
-      <c r="AE8" s="15"/>
-      <c r="AF8" s="15"/>
-      <c r="AG8" s="15"/>
-      <c r="AH8" s="15"/>
-      <c r="AI8" s="15"/>
-      <c r="AJ8" s="15"/>
-      <c r="AK8" s="15"/>
       <c r="AL8" s="15"/>
       <c r="AM8" s="15"/>
       <c r="AN8" s="15"/>
@@ -2277,8 +2401,15 @@
       <c r="DV8" s="15"/>
       <c r="DW8" s="15"/>
       <c r="DX8" s="15"/>
+      <c r="DY8" s="15"/>
+      <c r="DZ8" s="15"/>
+      <c r="EA8" s="15"/>
+      <c r="EB8" s="15"/>
+      <c r="EC8" s="15"/>
+      <c r="ED8" s="15"/>
+      <c r="EE8" s="15"/>
     </row>
-    <row r="9" spans="1:128" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:135" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="17">
         <v>1.2260241731999999</v>
       </c>
@@ -2367,23 +2498,23 @@
         <v>0.20261347408487851</v>
       </c>
       <c r="AB9" s="16" cm="1">
-        <f t="array" ref="AB9">SQRT(SUMPRODUCT(((J9:O9-P9:U9)/$AE$3:$AJ$3)^2)/6)*100</f>
+        <f t="array" ref="AB9">SQRT(SUMPRODUCT(((J9:O9-P9:U9)/$AL$3:$AQ$3)^2)/6)*100</f>
         <v>0.99186108018374397</v>
       </c>
-      <c r="AC9" s="5">
+      <c r="AC9" s="16"/>
+      <c r="AD9" s="16"/>
+      <c r="AE9" s="16"/>
+      <c r="AF9" s="16"/>
+      <c r="AG9" s="16"/>
+      <c r="AH9" s="16"/>
+      <c r="AI9" s="16"/>
+      <c r="AJ9" s="5">
         <f t="shared" si="7"/>
         <v>0.16</v>
       </c>
-      <c r="AD9" s="13">
+      <c r="AK9" s="13">
         <v>977.362718776885</v>
       </c>
-      <c r="AE9" s="15"/>
-      <c r="AF9" s="15"/>
-      <c r="AG9" s="15"/>
-      <c r="AH9" s="15"/>
-      <c r="AI9" s="15"/>
-      <c r="AJ9" s="15"/>
-      <c r="AK9" s="15"/>
       <c r="AL9" s="15"/>
       <c r="AM9" s="15"/>
       <c r="AN9" s="15"/>
@@ -2475,8 +2606,15 @@
       <c r="DV9" s="15"/>
       <c r="DW9" s="15"/>
       <c r="DX9" s="15"/>
+      <c r="DY9" s="15"/>
+      <c r="DZ9" s="15"/>
+      <c r="EA9" s="15"/>
+      <c r="EB9" s="15"/>
+      <c r="EC9" s="15"/>
+      <c r="ED9" s="15"/>
+      <c r="EE9" s="15"/>
     </row>
-    <row r="10" spans="1:128" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:135" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="17">
         <v>1.4922792275000001</v>
       </c>
@@ -2565,23 +2703,23 @@
         <v>8.870994356166384E-2</v>
       </c>
       <c r="AB10" s="16" cm="1">
-        <f t="array" ref="AB10">SQRT(SUMPRODUCT(((J10:O10-P10:U10)/$AE$3:$AJ$3)^2)/6)*100</f>
+        <f t="array" ref="AB10">SQRT(SUMPRODUCT(((J10:O10-P10:U10)/$AL$3:$AQ$3)^2)/6)*100</f>
         <v>1.0895940533020496</v>
       </c>
-      <c r="AC10" s="5">
+      <c r="AC10" s="16"/>
+      <c r="AD10" s="16"/>
+      <c r="AE10" s="16"/>
+      <c r="AF10" s="16"/>
+      <c r="AG10" s="16"/>
+      <c r="AH10" s="16"/>
+      <c r="AI10" s="16"/>
+      <c r="AJ10" s="5">
         <f t="shared" si="7"/>
         <v>0.16</v>
       </c>
-      <c r="AD10" s="13">
+      <c r="AK10" s="13">
         <v>827.55067436062598</v>
       </c>
-      <c r="AE10" s="15"/>
-      <c r="AF10" s="15"/>
-      <c r="AG10" s="15"/>
-      <c r="AH10" s="15"/>
-      <c r="AI10" s="15"/>
-      <c r="AJ10" s="15"/>
-      <c r="AK10" s="15"/>
       <c r="AL10" s="15"/>
       <c r="AM10" s="15"/>
       <c r="AN10" s="15"/>
@@ -2673,8 +2811,15 @@
       <c r="DV10" s="15"/>
       <c r="DW10" s="15"/>
       <c r="DX10" s="15"/>
+      <c r="DY10" s="15"/>
+      <c r="DZ10" s="15"/>
+      <c r="EA10" s="15"/>
+      <c r="EB10" s="15"/>
+      <c r="EC10" s="15"/>
+      <c r="ED10" s="15"/>
+      <c r="EE10" s="15"/>
     </row>
-    <row r="11" spans="1:128" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:135" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="17">
         <v>1.4258680059</v>
       </c>
@@ -2763,18 +2908,25 @@
         <v>7.7999939547981567E-2</v>
       </c>
       <c r="AB11" s="16" cm="1">
-        <f t="array" ref="AB11">SQRT(SUMPRODUCT(((J11:O11-P11:U11)/$AE$3:$AJ$3)^2)/6)*100</f>
+        <f t="array" ref="AB11">SQRT(SUMPRODUCT(((J11:O11-P11:U11)/$AL$3:$AQ$3)^2)/6)*100</f>
         <v>0.50734654492891529</v>
       </c>
-      <c r="AC11" s="5">
+      <c r="AC11" s="16"/>
+      <c r="AD11" s="16"/>
+      <c r="AE11" s="16"/>
+      <c r="AF11" s="16"/>
+      <c r="AG11" s="16"/>
+      <c r="AH11" s="16"/>
+      <c r="AI11" s="16"/>
+      <c r="AJ11" s="5">
         <f t="shared" si="7"/>
         <v>0.16</v>
       </c>
-      <c r="AD11" s="13">
+      <c r="AK11" s="13">
         <v>2387.7694271646001</v>
       </c>
     </row>
-    <row r="12" spans="1:128" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:135" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="17">
         <v>1.2847663906</v>
       </c>
@@ -2863,18 +3015,25 @@
         <v>-0.1600304971149358</v>
       </c>
       <c r="AB12" s="16" cm="1">
-        <f t="array" ref="AB12">SQRT(SUMPRODUCT(((J12:O12-P12:U12)/$AE$3:$AJ$3)^2)/6)*100</f>
+        <f t="array" ref="AB12">SQRT(SUMPRODUCT(((J12:O12-P12:U12)/$AL$3:$AQ$3)^2)/6)*100</f>
         <v>0.56299562359491806</v>
       </c>
-      <c r="AC12" s="5">
+      <c r="AC12" s="16"/>
+      <c r="AD12" s="16"/>
+      <c r="AE12" s="16"/>
+      <c r="AF12" s="16"/>
+      <c r="AG12" s="16"/>
+      <c r="AH12" s="16"/>
+      <c r="AI12" s="16"/>
+      <c r="AJ12" s="5">
         <f t="shared" si="7"/>
         <v>0.13999999999999999</v>
       </c>
-      <c r="AD12" s="13">
+      <c r="AK12" s="13">
         <v>378.090422116365</v>
       </c>
     </row>
-    <row r="13" spans="1:128" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:135" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="17">
         <v>0.82078888689999996</v>
       </c>
@@ -2963,18 +3122,25 @@
         <v>5.4767922598118385E-2</v>
       </c>
       <c r="AB13" s="16" cm="1">
-        <f t="array" ref="AB13">SQRT(SUMPRODUCT(((J13:O13-P13:U13)/$AE$3:$AJ$3)^2)/6)*100</f>
+        <f t="array" ref="AB13">SQRT(SUMPRODUCT(((J13:O13-P13:U13)/$AL$3:$AQ$3)^2)/6)*100</f>
         <v>0.5787798444406641</v>
       </c>
-      <c r="AC13" s="5">
+      <c r="AC13" s="16"/>
+      <c r="AD13" s="16"/>
+      <c r="AE13" s="16"/>
+      <c r="AF13" s="16"/>
+      <c r="AG13" s="16"/>
+      <c r="AH13" s="16"/>
+      <c r="AI13" s="16"/>
+      <c r="AJ13" s="5">
         <f t="shared" si="7"/>
         <v>0.13999999999999999</v>
       </c>
-      <c r="AD13" s="13">
+      <c r="AK13" s="13">
         <v>469.58688274687501</v>
       </c>
     </row>
-    <row r="14" spans="1:128" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:135" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="17">
         <v>0.51355824630000002</v>
       </c>
@@ -3063,18 +3229,25 @@
         <v>-3.0373116172602743E-2</v>
       </c>
       <c r="AB14" s="16" cm="1">
-        <f t="array" ref="AB14">SQRT(SUMPRODUCT(((J14:O14-P14:U14)/$AE$3:$AJ$3)^2)/6)*100</f>
+        <f t="array" ref="AB14">SQRT(SUMPRODUCT(((J14:O14-P14:U14)/$AL$3:$AQ$3)^2)/6)*100</f>
         <v>0.62589691860387442</v>
       </c>
-      <c r="AC14" s="5">
+      <c r="AC14" s="16"/>
+      <c r="AD14" s="16"/>
+      <c r="AE14" s="16"/>
+      <c r="AF14" s="16"/>
+      <c r="AG14" s="16"/>
+      <c r="AH14" s="16"/>
+      <c r="AI14" s="16"/>
+      <c r="AJ14" s="5">
         <f t="shared" si="7"/>
         <v>0.14000000000000001</v>
       </c>
-      <c r="AD14" s="13">
+      <c r="AK14" s="13">
         <v>496.63892383411002</v>
       </c>
     </row>
-    <row r="15" spans="1:128" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:135" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="17">
         <v>0.35944564579999999</v>
       </c>
@@ -3163,18 +3336,25 @@
         <v>7.7772348182451267E-2</v>
       </c>
       <c r="AB15" s="16" cm="1">
-        <f t="array" ref="AB15">SQRT(SUMPRODUCT(((J15:O15-P15:U15)/$AE$3:$AJ$3)^2)/6)*100</f>
+        <f t="array" ref="AB15">SQRT(SUMPRODUCT(((J15:O15-P15:U15)/$AL$3:$AQ$3)^2)/6)*100</f>
         <v>0.33820700264764636</v>
       </c>
-      <c r="AC15" s="5">
+      <c r="AC15" s="16"/>
+      <c r="AD15" s="16"/>
+      <c r="AE15" s="16"/>
+      <c r="AF15" s="16"/>
+      <c r="AG15" s="16"/>
+      <c r="AH15" s="16"/>
+      <c r="AI15" s="16"/>
+      <c r="AJ15" s="5">
         <f t="shared" si="7"/>
         <v>0.13999999999999999</v>
       </c>
-      <c r="AD15" s="13">
+      <c r="AK15" s="13">
         <v>2739.2714644073799</v>
       </c>
     </row>
-    <row r="16" spans="1:128" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:135" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="17">
         <v>1.2267525763</v>
       </c>
@@ -3263,18 +3443,25 @@
         <v>0.15803344244965545</v>
       </c>
       <c r="AB16" s="16" cm="1">
-        <f t="array" ref="AB16">SQRT(SUMPRODUCT(((J16:O16-P16:U16)/$AE$3:$AJ$3)^2)/6)*100</f>
+        <f t="array" ref="AB16">SQRT(SUMPRODUCT(((J16:O16-P16:U16)/$AL$3:$AQ$3)^2)/6)*100</f>
         <v>0.57611294365844889</v>
       </c>
-      <c r="AC16" s="5">
+      <c r="AC16" s="16"/>
+      <c r="AD16" s="16"/>
+      <c r="AE16" s="16"/>
+      <c r="AF16" s="16"/>
+      <c r="AG16" s="16"/>
+      <c r="AH16" s="16"/>
+      <c r="AI16" s="16"/>
+      <c r="AJ16" s="5">
         <f t="shared" si="7"/>
         <v>0.12</v>
       </c>
-      <c r="AD16" s="13">
+      <c r="AK16" s="13">
         <v>231.264969730491</v>
       </c>
     </row>
-    <row r="17" spans="1:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="17">
         <v>0.64421489080000005</v>
       </c>
@@ -3363,18 +3550,25 @@
         <v>-6.688445355823025E-2</v>
       </c>
       <c r="AB17" s="16" cm="1">
-        <f t="array" ref="AB17">SQRT(SUMPRODUCT(((J17:O17-P17:U17)/$AE$3:$AJ$3)^2)/6)*100</f>
+        <f t="array" ref="AB17">SQRT(SUMPRODUCT(((J17:O17-P17:U17)/$AL$3:$AQ$3)^2)/6)*100</f>
         <v>0.30621501935206624</v>
       </c>
-      <c r="AC17" s="5">
+      <c r="AC17" s="16"/>
+      <c r="AD17" s="16"/>
+      <c r="AE17" s="16"/>
+      <c r="AF17" s="16"/>
+      <c r="AG17" s="16"/>
+      <c r="AH17" s="16"/>
+      <c r="AI17" s="16"/>
+      <c r="AJ17" s="5">
         <f t="shared" si="7"/>
         <v>0.12000000000000001</v>
       </c>
-      <c r="AD17" s="13">
+      <c r="AK17" s="13">
         <v>437.69063130900997</v>
       </c>
     </row>
-    <row r="18" spans="1:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="17">
         <v>1.1302547975999999</v>
       </c>
@@ -3463,18 +3657,25 @@
         <v>0.18628371541768418</v>
       </c>
       <c r="AB18" s="16" cm="1">
-        <f t="array" ref="AB18">SQRT(SUMPRODUCT(((J18:O18-P18:U18)/$AE$3:$AJ$3)^2)/6)*100</f>
+        <f t="array" ref="AB18">SQRT(SUMPRODUCT(((J18:O18-P18:U18)/$AL$3:$AQ$3)^2)/6)*100</f>
         <v>0.54894256347205461</v>
       </c>
-      <c r="AC18" s="5">
+      <c r="AC18" s="16"/>
+      <c r="AD18" s="16"/>
+      <c r="AE18" s="16"/>
+      <c r="AF18" s="16"/>
+      <c r="AG18" s="16"/>
+      <c r="AH18" s="16"/>
+      <c r="AI18" s="16"/>
+      <c r="AJ18" s="5">
         <f t="shared" si="7"/>
         <v>0.12</v>
       </c>
-      <c r="AD18" s="13">
+      <c r="AK18" s="13">
         <v>805.85456510326605</v>
       </c>
     </row>
-    <row r="19" spans="1:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="17">
         <v>0.44052297210000002</v>
       </c>
@@ -3563,18 +3764,25 @@
         <v>4.093820937682574E-2</v>
       </c>
       <c r="AB19" s="16" cm="1">
-        <f t="array" ref="AB19">SQRT(SUMPRODUCT(((J19:O19-P19:U19)/$AE$3:$AJ$3)^2)/6)*100</f>
+        <f t="array" ref="AB19">SQRT(SUMPRODUCT(((J19:O19-P19:U19)/$AL$3:$AQ$3)^2)/6)*100</f>
         <v>0.5238184031041222</v>
       </c>
-      <c r="AC19" s="5">
+      <c r="AC19" s="16"/>
+      <c r="AD19" s="16"/>
+      <c r="AE19" s="16"/>
+      <c r="AF19" s="16"/>
+      <c r="AG19" s="16"/>
+      <c r="AH19" s="16"/>
+      <c r="AI19" s="16"/>
+      <c r="AJ19" s="5">
         <f t="shared" si="7"/>
         <v>0.12000000000000001</v>
       </c>
-      <c r="AD19" s="13">
+      <c r="AK19" s="13">
         <v>1423.74196433815</v>
       </c>
     </row>
-    <row r="20" spans="1:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="17">
         <v>1.4424756030000001</v>
       </c>
@@ -3663,18 +3871,25 @@
         <v>-3.8889977467147174E-2</v>
       </c>
       <c r="AB20" s="16" cm="1">
-        <f t="array" ref="AB20">SQRT(SUMPRODUCT(((J20:O20-P20:U20)/$AE$3:$AJ$3)^2)/6)*100</f>
+        <f t="array" ref="AB20">SQRT(SUMPRODUCT(((J20:O20-P20:U20)/$AL$3:$AQ$3)^2)/6)*100</f>
         <v>0.79795452595788874</v>
       </c>
-      <c r="AC20" s="5">
+      <c r="AC20" s="16"/>
+      <c r="AD20" s="16"/>
+      <c r="AE20" s="16"/>
+      <c r="AF20" s="16"/>
+      <c r="AG20" s="16"/>
+      <c r="AH20" s="16"/>
+      <c r="AI20" s="16"/>
+      <c r="AJ20" s="5">
         <f t="shared" si="7"/>
         <v>0.12</v>
       </c>
-      <c r="AD20" s="13">
+      <c r="AK20" s="13">
         <v>308.16246208647402</v>
       </c>
     </row>
-    <row r="21" spans="1:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="17">
         <v>1.3085202701</v>
       </c>
@@ -3763,18 +3978,25 @@
         <v>1.5288530681038415E-2</v>
       </c>
       <c r="AB21" s="16" cm="1">
-        <f t="array" ref="AB21">SQRT(SUMPRODUCT(((J21:O21-P21:U21)/$AE$3:$AJ$3)^2)/6)*100</f>
+        <f t="array" ref="AB21">SQRT(SUMPRODUCT(((J21:O21-P21:U21)/$AL$3:$AQ$3)^2)/6)*100</f>
         <v>0.66215914991896585</v>
       </c>
-      <c r="AC21" s="5">
+      <c r="AC21" s="16"/>
+      <c r="AD21" s="16"/>
+      <c r="AE21" s="16"/>
+      <c r="AF21" s="16"/>
+      <c r="AG21" s="16"/>
+      <c r="AH21" s="16"/>
+      <c r="AI21" s="16"/>
+      <c r="AJ21" s="5">
         <f t="shared" si="7"/>
         <v>0.12000000000000001</v>
       </c>
-      <c r="AD21" s="13">
+      <c r="AK21" s="13">
         <v>1514.3525859680799</v>
       </c>
     </row>
-    <row r="22" spans="1:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="17">
         <v>1.0278031490999999</v>
       </c>
@@ -3863,18 +4085,25 @@
         <v>-5.2985212706684326E-3</v>
       </c>
       <c r="AB22" s="16" cm="1">
-        <f t="array" ref="AB22">SQRT(SUMPRODUCT(((J22:O22-P22:U22)/$AE$3:$AJ$3)^2)/6)*100</f>
+        <f t="array" ref="AB22">SQRT(SUMPRODUCT(((J22:O22-P22:U22)/$AL$3:$AQ$3)^2)/6)*100</f>
         <v>0.7547820223524403</v>
       </c>
-      <c r="AC22" s="5">
+      <c r="AC22" s="16"/>
+      <c r="AD22" s="16"/>
+      <c r="AE22" s="16"/>
+      <c r="AF22" s="16"/>
+      <c r="AG22" s="16"/>
+      <c r="AH22" s="16"/>
+      <c r="AI22" s="16"/>
+      <c r="AJ22" s="5">
         <f t="shared" si="7"/>
         <v>0.1</v>
       </c>
-      <c r="AD22" s="13">
+      <c r="AK22" s="13">
         <v>3474.0972684693302</v>
       </c>
     </row>
-    <row r="23" spans="1:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="17">
         <v>0.8908774062</v>
       </c>
@@ -3963,18 +4192,25 @@
         <v>4.3169320426073243E-2</v>
       </c>
       <c r="AB23" s="16" cm="1">
-        <f t="array" ref="AB23">SQRT(SUMPRODUCT(((J23:O23-P23:U23)/$AE$3:$AJ$3)^2)/6)*100</f>
+        <f t="array" ref="AB23">SQRT(SUMPRODUCT(((J23:O23-P23:U23)/$AL$3:$AQ$3)^2)/6)*100</f>
         <v>0.26527692899206096</v>
       </c>
-      <c r="AC23" s="5">
+      <c r="AC23" s="16"/>
+      <c r="AD23" s="16"/>
+      <c r="AE23" s="16"/>
+      <c r="AF23" s="16"/>
+      <c r="AG23" s="16"/>
+      <c r="AH23" s="16"/>
+      <c r="AI23" s="16"/>
+      <c r="AJ23" s="5">
         <f t="shared" si="7"/>
         <v>9.9999999999999992E-2</v>
       </c>
-      <c r="AD23" s="13">
+      <c r="AK23" s="13">
         <v>864.30675856593803</v>
       </c>
     </row>
-    <row r="24" spans="1:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="17">
         <v>1.2597568109999999</v>
       </c>
@@ -4063,18 +4299,25 @@
         <v>-8.7381331073741464E-3</v>
       </c>
       <c r="AB24" s="16" cm="1">
-        <f t="array" ref="AB24">SQRT(SUMPRODUCT(((J24:O24-P24:U24)/$AE$3:$AJ$3)^2)/6)*100</f>
+        <f t="array" ref="AB24">SQRT(SUMPRODUCT(((J24:O24-P24:U24)/$AL$3:$AQ$3)^2)/6)*100</f>
         <v>0.90861878220752335</v>
       </c>
-      <c r="AC24" s="5">
+      <c r="AC24" s="16"/>
+      <c r="AD24" s="16"/>
+      <c r="AE24" s="16"/>
+      <c r="AF24" s="16"/>
+      <c r="AG24" s="16"/>
+      <c r="AH24" s="16"/>
+      <c r="AI24" s="16"/>
+      <c r="AJ24" s="5">
         <f t="shared" si="7"/>
         <v>0.1</v>
       </c>
-      <c r="AD24" s="13">
+      <c r="AK24" s="13">
         <v>1340.77907487627</v>
       </c>
     </row>
-    <row r="25" spans="1:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="17">
         <v>0.65858340790000003</v>
       </c>
@@ -4163,18 +4406,25 @@
         <v>3.9610111827364125E-2</v>
       </c>
       <c r="AB25" s="16" cm="1">
-        <f t="array" ref="AB25">SQRT(SUMPRODUCT(((J25:O25-P25:U25)/$AE$3:$AJ$3)^2)/6)*100</f>
+        <f t="array" ref="AB25">SQRT(SUMPRODUCT(((J25:O25-P25:U25)/$AL$3:$AQ$3)^2)/6)*100</f>
         <v>0.54864288522978644</v>
       </c>
-      <c r="AC25" s="5">
+      <c r="AC25" s="16"/>
+      <c r="AD25" s="16"/>
+      <c r="AE25" s="16"/>
+      <c r="AF25" s="16"/>
+      <c r="AG25" s="16"/>
+      <c r="AH25" s="16"/>
+      <c r="AI25" s="16"/>
+      <c r="AJ25" s="5">
         <f t="shared" si="7"/>
         <v>9.9999999999999992E-2</v>
       </c>
-      <c r="AD25" s="13">
+      <c r="AK25" s="13">
         <v>35245.690684348701</v>
       </c>
     </row>
-    <row r="26" spans="1:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="17">
         <v>0.55032038400000005</v>
       </c>
@@ -4263,18 +4513,25 @@
         <v>7.3260386474459649E-2</v>
       </c>
       <c r="AB26" s="16" cm="1">
-        <f t="array" ref="AB26">SQRT(SUMPRODUCT(((J26:O26-P26:U26)/$AE$3:$AJ$3)^2)/6)*100</f>
+        <f t="array" ref="AB26">SQRT(SUMPRODUCT(((J26:O26-P26:U26)/$AL$3:$AQ$3)^2)/6)*100</f>
         <v>0.64698744866027846</v>
       </c>
-      <c r="AC26" s="5">
+      <c r="AC26" s="16"/>
+      <c r="AD26" s="16"/>
+      <c r="AE26" s="16"/>
+      <c r="AF26" s="16"/>
+      <c r="AG26" s="16"/>
+      <c r="AH26" s="16"/>
+      <c r="AI26" s="16"/>
+      <c r="AJ26" s="5">
         <f t="shared" si="7"/>
         <v>0.08</v>
       </c>
-      <c r="AD26" s="13">
+      <c r="AK26" s="13">
         <v>789.51379310088396</v>
       </c>
     </row>
-    <row r="27" spans="1:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="17">
         <v>1.2531062278</v>
       </c>
@@ -4363,18 +4620,25 @@
         <v>-0.10436282332739744</v>
       </c>
       <c r="AB27" s="16" cm="1">
-        <f t="array" ref="AB27">SQRT(SUMPRODUCT(((J27:O27-P27:U27)/$AE$3:$AJ$3)^2)/6)*100</f>
+        <f t="array" ref="AB27">SQRT(SUMPRODUCT(((J27:O27-P27:U27)/$AL$3:$AQ$3)^2)/6)*100</f>
         <v>0.99811060299720089</v>
       </c>
-      <c r="AC27" s="5">
+      <c r="AC27" s="16"/>
+      <c r="AD27" s="16"/>
+      <c r="AE27" s="16"/>
+      <c r="AF27" s="16"/>
+      <c r="AG27" s="16"/>
+      <c r="AH27" s="16"/>
+      <c r="AI27" s="16"/>
+      <c r="AJ27" s="5">
         <f t="shared" si="7"/>
         <v>7.9999999999999988E-2</v>
       </c>
-      <c r="AD27" s="13">
+      <c r="AK27" s="13">
         <v>438.17087927725402</v>
       </c>
     </row>
-    <row r="28" spans="1:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="17">
         <v>0.37674236639999997</v>
       </c>
@@ -4463,18 +4727,25 @@
         <v>0.12643878449992496</v>
       </c>
       <c r="AB28" s="16" cm="1">
-        <f t="array" ref="AB28">SQRT(SUMPRODUCT(((J28:O28-P28:U28)/$AE$3:$AJ$3)^2)/6)*100</f>
+        <f t="array" ref="AB28">SQRT(SUMPRODUCT(((J28:O28-P28:U28)/$AL$3:$AQ$3)^2)/6)*100</f>
         <v>0.40336156011742613</v>
       </c>
-      <c r="AC28" s="5">
+      <c r="AC28" s="16"/>
+      <c r="AD28" s="16"/>
+      <c r="AE28" s="16"/>
+      <c r="AF28" s="16"/>
+      <c r="AG28" s="16"/>
+      <c r="AH28" s="16"/>
+      <c r="AI28" s="16"/>
+      <c r="AJ28" s="5">
         <f t="shared" si="7"/>
         <v>7.9999999999999988E-2</v>
       </c>
-      <c r="AD28" s="13">
+      <c r="AK28" s="13">
         <v>3753.46837280214</v>
       </c>
     </row>
-    <row r="29" spans="1:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="17">
         <v>0.99744538530000004</v>
       </c>
@@ -4563,18 +4834,25 @@
         <v>-8.7327855187650197E-2</v>
       </c>
       <c r="AB29" s="16" cm="1">
-        <f t="array" ref="AB29">SQRT(SUMPRODUCT(((J29:O29-P29:U29)/$AE$3:$AJ$3)^2)/6)*100</f>
+        <f t="array" ref="AB29">SQRT(SUMPRODUCT(((J29:O29-P29:U29)/$AL$3:$AQ$3)^2)/6)*100</f>
         <v>0.32621462877144874</v>
       </c>
-      <c r="AC29" s="5">
+      <c r="AC29" s="16"/>
+      <c r="AD29" s="16"/>
+      <c r="AE29" s="16"/>
+      <c r="AF29" s="16"/>
+      <c r="AG29" s="16"/>
+      <c r="AH29" s="16"/>
+      <c r="AI29" s="16"/>
+      <c r="AJ29" s="5">
         <f t="shared" si="7"/>
         <v>7.9999999999999988E-2</v>
       </c>
-      <c r="AD29" s="13">
+      <c r="AK29" s="13">
         <v>7584.2432871298897</v>
       </c>
     </row>
-    <row r="30" spans="1:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="17">
         <v>0.91958396450000002</v>
       </c>
@@ -4663,18 +4941,25 @@
         <v>-6.8292166981305247E-3</v>
       </c>
       <c r="AB30" s="16" cm="1">
-        <f t="array" ref="AB30">SQRT(SUMPRODUCT(((J30:O30-P30:U30)/$AE$3:$AJ$3)^2)/6)*100</f>
+        <f t="array" ref="AB30">SQRT(SUMPRODUCT(((J30:O30-P30:U30)/$AL$3:$AQ$3)^2)/6)*100</f>
         <v>1.0214940432633177</v>
       </c>
-      <c r="AC30" s="5">
+      <c r="AC30" s="16"/>
+      <c r="AD30" s="16"/>
+      <c r="AE30" s="16"/>
+      <c r="AF30" s="16"/>
+      <c r="AG30" s="16"/>
+      <c r="AH30" s="16"/>
+      <c r="AI30" s="16"/>
+      <c r="AJ30" s="5">
         <f t="shared" si="7"/>
         <v>7.9999999999999988E-2</v>
       </c>
-      <c r="AD30" s="13">
+      <c r="AK30" s="13">
         <v>1265.9910463044</v>
       </c>
     </row>
-    <row r="31" spans="1:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="17">
         <v>0.76015027209999997</v>
       </c>
@@ -4763,18 +5048,25 @@
         <v>-1.4066270106979195E-2</v>
       </c>
       <c r="AB31" s="16" cm="1">
-        <f t="array" ref="AB31">SQRT(SUMPRODUCT(((J31:O31-P31:U31)/$AE$3:$AJ$3)^2)/6)*100</f>
+        <f t="array" ref="AB31">SQRT(SUMPRODUCT(((J31:O31-P31:U31)/$AL$3:$AQ$3)^2)/6)*100</f>
         <v>0.92175627991106601</v>
       </c>
-      <c r="AC31" s="5">
+      <c r="AC31" s="16"/>
+      <c r="AD31" s="16"/>
+      <c r="AE31" s="16"/>
+      <c r="AF31" s="16"/>
+      <c r="AG31" s="16"/>
+      <c r="AH31" s="16"/>
+      <c r="AI31" s="16"/>
+      <c r="AJ31" s="5">
         <f t="shared" si="7"/>
         <v>7.9999999999999988E-2</v>
       </c>
-      <c r="AD31" s="13">
+      <c r="AK31" s="13">
         <v>435.17861473415201</v>
       </c>
     </row>
-    <row r="32" spans="1:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="17">
         <v>0.9040684336</v>
       </c>
@@ -4863,18 +5155,25 @@
         <v>-5.59416876725225E-2</v>
       </c>
       <c r="AB32" s="16" cm="1">
-        <f t="array" ref="AB32">SQRT(SUMPRODUCT(((J32:O32-P32:U32)/$AE$3:$AJ$3)^2)/6)*100</f>
+        <f t="array" ref="AB32">SQRT(SUMPRODUCT(((J32:O32-P32:U32)/$AL$3:$AQ$3)^2)/6)*100</f>
         <v>0.25673377199705427</v>
       </c>
-      <c r="AC32" s="5">
+      <c r="AC32" s="16"/>
+      <c r="AD32" s="16"/>
+      <c r="AE32" s="16"/>
+      <c r="AF32" s="16"/>
+      <c r="AG32" s="16"/>
+      <c r="AH32" s="16"/>
+      <c r="AI32" s="16"/>
+      <c r="AJ32" s="5">
         <f t="shared" si="7"/>
         <v>0.08</v>
       </c>
-      <c r="AD32" s="13">
+      <c r="AK32" s="13">
         <v>1388.8921224230301</v>
       </c>
     </row>
-    <row r="33" spans="1:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="17">
         <v>1.4109779404</v>
       </c>
@@ -4963,18 +5262,25 @@
         <v>7.1349923646898863E-2</v>
       </c>
       <c r="AB33" s="16" cm="1">
-        <f t="array" ref="AB33">SQRT(SUMPRODUCT(((J33:O33-P33:U33)/$AE$3:$AJ$3)^2)/6)*100</f>
+        <f t="array" ref="AB33">SQRT(SUMPRODUCT(((J33:O33-P33:U33)/$AL$3:$AQ$3)^2)/6)*100</f>
         <v>1.5052725331492411</v>
       </c>
-      <c r="AC33" s="5">
+      <c r="AC33" s="16"/>
+      <c r="AD33" s="16"/>
+      <c r="AE33" s="16"/>
+      <c r="AF33" s="16"/>
+      <c r="AG33" s="16"/>
+      <c r="AH33" s="16"/>
+      <c r="AI33" s="16"/>
+      <c r="AJ33" s="5">
         <f t="shared" si="7"/>
         <v>8.0000000000000016E-2</v>
       </c>
-      <c r="AD33" s="13">
+      <c r="AK33" s="13">
         <v>1378.60874175766</v>
       </c>
     </row>
-    <row r="34" spans="1:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="17">
         <v>1.4747736548999999</v>
       </c>
@@ -5063,18 +5369,25 @@
         <v>0.10515849434172803</v>
       </c>
       <c r="AB34" s="16" cm="1">
-        <f t="array" ref="AB34">SQRT(SUMPRODUCT(((J34:O34-P34:U34)/$AE$3:$AJ$3)^2)/6)*100</f>
+        <f t="array" ref="AB34">SQRT(SUMPRODUCT(((J34:O34-P34:U34)/$AL$3:$AQ$3)^2)/6)*100</f>
         <v>1.7504861436935728</v>
       </c>
-      <c r="AC34" s="5">
+      <c r="AC34" s="16"/>
+      <c r="AD34" s="16"/>
+      <c r="AE34" s="16"/>
+      <c r="AF34" s="16"/>
+      <c r="AG34" s="16"/>
+      <c r="AH34" s="16"/>
+      <c r="AI34" s="16"/>
+      <c r="AJ34" s="5">
         <f t="shared" si="7"/>
         <v>8.0000000000000016E-2</v>
       </c>
-      <c r="AD34" s="13">
+      <c r="AK34" s="13">
         <v>1674.85682889344</v>
       </c>
     </row>
-    <row r="35" spans="1:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="17">
         <v>1.1341222659000001</v>
       </c>
@@ -5163,18 +5476,25 @@
         <v>-8.3383676520175865E-2</v>
       </c>
       <c r="AB35" s="16" cm="1">
-        <f t="array" ref="AB35">SQRT(SUMPRODUCT(((J35:O35-P35:U35)/$AE$3:$AJ$3)^2)/6)*100</f>
+        <f t="array" ref="AB35">SQRT(SUMPRODUCT(((J35:O35-P35:U35)/$AL$3:$AQ$3)^2)/6)*100</f>
         <v>0.36131638388173104</v>
       </c>
-      <c r="AC35" s="5">
+      <c r="AC35" s="16"/>
+      <c r="AD35" s="16"/>
+      <c r="AE35" s="16"/>
+      <c r="AF35" s="16"/>
+      <c r="AG35" s="16"/>
+      <c r="AH35" s="16"/>
+      <c r="AI35" s="16"/>
+      <c r="AJ35" s="5">
         <f t="shared" si="7"/>
         <v>7.9999999999999988E-2</v>
       </c>
-      <c r="AD35" s="13">
+      <c r="AK35" s="13">
         <v>9921.9837729904102</v>
       </c>
     </row>
-    <row r="36" spans="1:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="17">
         <v>0.785852255</v>
       </c>
@@ -5263,18 +5583,25 @@
         <v>-5.708442610012715E-2</v>
       </c>
       <c r="AB36" s="16" cm="1">
-        <f t="array" ref="AB36">SQRT(SUMPRODUCT(((J36:O36-P36:U36)/$AE$3:$AJ$3)^2)/6)*100</f>
+        <f t="array" ref="AB36">SQRT(SUMPRODUCT(((J36:O36-P36:U36)/$AL$3:$AQ$3)^2)/6)*100</f>
         <v>0.32814059724467248</v>
       </c>
-      <c r="AC36" s="5">
+      <c r="AC36" s="16"/>
+      <c r="AD36" s="16"/>
+      <c r="AE36" s="16"/>
+      <c r="AF36" s="16"/>
+      <c r="AG36" s="16"/>
+      <c r="AH36" s="16"/>
+      <c r="AI36" s="16"/>
+      <c r="AJ36" s="5">
         <f t="shared" si="7"/>
         <v>0.08</v>
       </c>
-      <c r="AD36" s="13">
+      <c r="AK36" s="13">
         <v>7047.4718615495003</v>
       </c>
     </row>
-    <row r="37" spans="1:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="17">
         <v>0.4787670047</v>
       </c>
@@ -5363,18 +5690,25 @@
         <v>8.0745237284346572E-2</v>
       </c>
       <c r="AB37" s="16" cm="1">
-        <f t="array" ref="AB37">SQRT(SUMPRODUCT(((J37:O37-P37:U37)/$AE$3:$AJ$3)^2)/6)*100</f>
+        <f t="array" ref="AB37">SQRT(SUMPRODUCT(((J37:O37-P37:U37)/$AL$3:$AQ$3)^2)/6)*100</f>
         <v>0.61941310827195095</v>
       </c>
-      <c r="AC37" s="5">
+      <c r="AC37" s="16"/>
+      <c r="AD37" s="16"/>
+      <c r="AE37" s="16"/>
+      <c r="AF37" s="16"/>
+      <c r="AG37" s="16"/>
+      <c r="AH37" s="16"/>
+      <c r="AI37" s="16"/>
+      <c r="AJ37" s="5">
         <f t="shared" si="7"/>
         <v>0.06</v>
       </c>
-      <c r="AD37" s="13">
+      <c r="AK37" s="13">
         <v>4885.3607236447197</v>
       </c>
     </row>
-    <row r="38" spans="1:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="17">
         <v>1.2825258852999999</v>
       </c>
@@ -5463,18 +5797,25 @@
         <v>-7.5969020157769629E-2</v>
       </c>
       <c r="AB38" s="16" cm="1">
-        <f t="array" ref="AB38">SQRT(SUMPRODUCT(((J38:O38-P38:U38)/$AE$3:$AJ$3)^2)/6)*100</f>
+        <f t="array" ref="AB38">SQRT(SUMPRODUCT(((J38:O38-P38:U38)/$AL$3:$AQ$3)^2)/6)*100</f>
         <v>0.88352820724630476</v>
       </c>
-      <c r="AC38" s="5">
+      <c r="AC38" s="16"/>
+      <c r="AD38" s="16"/>
+      <c r="AE38" s="16"/>
+      <c r="AF38" s="16"/>
+      <c r="AG38" s="16"/>
+      <c r="AH38" s="16"/>
+      <c r="AI38" s="16"/>
+      <c r="AJ38" s="5">
         <f t="shared" si="7"/>
         <v>6.0000000000000012E-2</v>
       </c>
-      <c r="AD38" s="13">
+      <c r="AK38" s="13">
         <v>1325.5370563973599</v>
       </c>
     </row>
-    <row r="39" spans="1:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="17">
         <v>1.0319949839</v>
       </c>
@@ -5563,18 +5904,25 @@
         <v>0.19625932734612306</v>
       </c>
       <c r="AB39" s="16" cm="1">
-        <f t="array" ref="AB39">SQRT(SUMPRODUCT(((J39:O39-P39:U39)/$AE$3:$AJ$3)^2)/6)*100</f>
+        <f t="array" ref="AB39">SQRT(SUMPRODUCT(((J39:O39-P39:U39)/$AL$3:$AQ$3)^2)/6)*100</f>
         <v>1.4449008065567992</v>
       </c>
-      <c r="AC39" s="5">
+      <c r="AC39" s="16"/>
+      <c r="AD39" s="16"/>
+      <c r="AE39" s="16"/>
+      <c r="AF39" s="16"/>
+      <c r="AG39" s="16"/>
+      <c r="AH39" s="16"/>
+      <c r="AI39" s="16"/>
+      <c r="AJ39" s="5">
         <f t="shared" si="7"/>
         <v>0.06</v>
       </c>
-      <c r="AD39" s="13">
+      <c r="AK39" s="13">
         <v>13498.249253091601</v>
       </c>
     </row>
-    <row r="40" spans="1:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="17">
         <v>0.54659396309999997</v>
       </c>
@@ -5663,18 +6011,25 @@
         <v>6.6825649504637138E-2</v>
       </c>
       <c r="AB40" s="16" cm="1">
-        <f t="array" ref="AB40">SQRT(SUMPRODUCT(((J40:O40-P40:U40)/$AE$3:$AJ$3)^2)/6)*100</f>
+        <f t="array" ref="AB40">SQRT(SUMPRODUCT(((J40:O40-P40:U40)/$AL$3:$AQ$3)^2)/6)*100</f>
         <v>0.31074045307739351</v>
       </c>
-      <c r="AC40" s="5">
+      <c r="AC40" s="16"/>
+      <c r="AD40" s="16"/>
+      <c r="AE40" s="16"/>
+      <c r="AF40" s="16"/>
+      <c r="AG40" s="16"/>
+      <c r="AH40" s="16"/>
+      <c r="AI40" s="16"/>
+      <c r="AJ40" s="5">
         <f t="shared" si="7"/>
         <v>6.0000000000000012E-2</v>
       </c>
-      <c r="AD40" s="13">
+      <c r="AK40" s="13">
         <v>2507.9697780861502</v>
       </c>
     </row>
-    <row r="41" spans="1:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="17">
         <v>0.62359206519999999</v>
       </c>
@@ -5763,18 +6118,25 @@
         <v>-5.2379287056978807E-2</v>
       </c>
       <c r="AB41" s="16" cm="1">
-        <f t="array" ref="AB41">SQRT(SUMPRODUCT(((J41:O41-P41:U41)/$AE$3:$AJ$3)^2)/6)*100</f>
+        <f t="array" ref="AB41">SQRT(SUMPRODUCT(((J41:O41-P41:U41)/$AL$3:$AQ$3)^2)/6)*100</f>
         <v>0.35677001836262456</v>
       </c>
-      <c r="AC41" s="5">
+      <c r="AC41" s="16"/>
+      <c r="AD41" s="16"/>
+      <c r="AE41" s="16"/>
+      <c r="AF41" s="16"/>
+      <c r="AG41" s="16"/>
+      <c r="AH41" s="16"/>
+      <c r="AI41" s="16"/>
+      <c r="AJ41" s="5">
         <f t="shared" si="7"/>
         <v>0.06</v>
       </c>
-      <c r="AD41" s="13">
+      <c r="AK41" s="13">
         <v>2696.32531405294</v>
       </c>
     </row>
-    <row r="42" spans="1:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="17">
         <v>1.3484992293</v>
       </c>
@@ -5863,18 +6225,25 @@
         <v>-2.2602209844056198E-2</v>
       </c>
       <c r="AB42" s="16" cm="1">
-        <f t="array" ref="AB42">SQRT(SUMPRODUCT(((J42:O42-P42:U42)/$AE$3:$AJ$3)^2)/6)*100</f>
+        <f t="array" ref="AB42">SQRT(SUMPRODUCT(((J42:O42-P42:U42)/$AL$3:$AQ$3)^2)/6)*100</f>
         <v>0.60761596509136739</v>
       </c>
-      <c r="AC42" s="5">
+      <c r="AC42" s="16"/>
+      <c r="AD42" s="16"/>
+      <c r="AE42" s="16"/>
+      <c r="AF42" s="16"/>
+      <c r="AG42" s="16"/>
+      <c r="AH42" s="16"/>
+      <c r="AI42" s="16"/>
+      <c r="AJ42" s="5">
         <f t="shared" si="7"/>
         <v>0.06</v>
       </c>
-      <c r="AD42" s="13">
+      <c r="AK42" s="13">
         <v>3302.7038748377799</v>
       </c>
     </row>
-    <row r="43" spans="1:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="17">
         <v>0.51681038229999998</v>
       </c>
@@ -5963,18 +6332,25 @@
         <v>-8.7120717786107749E-2</v>
       </c>
       <c r="AB43" s="16" cm="1">
-        <f t="array" ref="AB43">SQRT(SUMPRODUCT(((J43:O43-P43:U43)/$AE$3:$AJ$3)^2)/6)*100</f>
+        <f t="array" ref="AB43">SQRT(SUMPRODUCT(((J43:O43-P43:U43)/$AL$3:$AQ$3)^2)/6)*100</f>
         <v>0.31011376621129355</v>
       </c>
-      <c r="AC43" s="5">
+      <c r="AC43" s="16"/>
+      <c r="AD43" s="16"/>
+      <c r="AE43" s="16"/>
+      <c r="AF43" s="16"/>
+      <c r="AG43" s="16"/>
+      <c r="AH43" s="16"/>
+      <c r="AI43" s="16"/>
+      <c r="AJ43" s="5">
         <f t="shared" si="7"/>
         <v>0.06</v>
       </c>
-      <c r="AD43" s="13">
+      <c r="AK43" s="13">
         <v>1902.8805691713201</v>
       </c>
     </row>
-    <row r="44" spans="1:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="17">
         <v>0.68441694529999997</v>
       </c>
@@ -6063,18 +6439,25 @@
         <v>-3.7414530574482185E-2</v>
       </c>
       <c r="AB44" s="16" cm="1">
-        <f t="array" ref="AB44">SQRT(SUMPRODUCT(((J44:O44-P44:U44)/$AE$3:$AJ$3)^2)/6)*100</f>
+        <f t="array" ref="AB44">SQRT(SUMPRODUCT(((J44:O44-P44:U44)/$AL$3:$AQ$3)^2)/6)*100</f>
         <v>0.76557972720160727</v>
       </c>
-      <c r="AC44" s="5">
+      <c r="AC44" s="16"/>
+      <c r="AD44" s="16"/>
+      <c r="AE44" s="16"/>
+      <c r="AF44" s="16"/>
+      <c r="AG44" s="16"/>
+      <c r="AH44" s="16"/>
+      <c r="AI44" s="16"/>
+      <c r="AJ44" s="5">
         <f t="shared" si="7"/>
         <v>0.06</v>
       </c>
-      <c r="AD44" s="13">
+      <c r="AK44" s="13">
         <v>1899.84061373393</v>
       </c>
     </row>
-    <row r="45" spans="1:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="17">
         <v>1.3991334753</v>
       </c>
@@ -6163,18 +6546,25 @@
         <v>-0.12592240327699922</v>
       </c>
       <c r="AB45" s="16" cm="1">
-        <f t="array" ref="AB45">SQRT(SUMPRODUCT(((J45:O45-P45:U45)/$AE$3:$AJ$3)^2)/6)*100</f>
+        <f t="array" ref="AB45">SQRT(SUMPRODUCT(((J45:O45-P45:U45)/$AL$3:$AQ$3)^2)/6)*100</f>
         <v>0.65665945921472169</v>
       </c>
-      <c r="AC45" s="5">
+      <c r="AC45" s="16"/>
+      <c r="AD45" s="16"/>
+      <c r="AE45" s="16"/>
+      <c r="AF45" s="16"/>
+      <c r="AG45" s="16"/>
+      <c r="AH45" s="16"/>
+      <c r="AI45" s="16"/>
+      <c r="AJ45" s="5">
         <f t="shared" si="7"/>
         <v>0.06</v>
       </c>
-      <c r="AD45" s="13">
+      <c r="AK45" s="13">
         <v>3531.6212508260901</v>
       </c>
     </row>
-    <row r="46" spans="1:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="17">
         <v>0.4668308846</v>
       </c>
@@ -6263,18 +6653,25 @@
         <v>-1.8268450851181006E-2</v>
       </c>
       <c r="AB46" s="16" cm="1">
-        <f t="array" ref="AB46">SQRT(SUMPRODUCT(((J46:O46-P46:U46)/$AE$3:$AJ$3)^2)/6)*100</f>
+        <f t="array" ref="AB46">SQRT(SUMPRODUCT(((J46:O46-P46:U46)/$AL$3:$AQ$3)^2)/6)*100</f>
         <v>0.24998078839917254</v>
       </c>
-      <c r="AC46" s="5">
+      <c r="AC46" s="16"/>
+      <c r="AD46" s="16"/>
+      <c r="AE46" s="16"/>
+      <c r="AF46" s="16"/>
+      <c r="AG46" s="16"/>
+      <c r="AH46" s="16"/>
+      <c r="AI46" s="16"/>
+      <c r="AJ46" s="5">
         <f t="shared" si="7"/>
         <v>0.04</v>
       </c>
-      <c r="AD46" s="13">
+      <c r="AK46" s="13">
         <v>2113.8744242274001</v>
       </c>
     </row>
-    <row r="47" spans="1:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="17">
         <v>1.4827422800000001</v>
       </c>
@@ -6363,18 +6760,25 @@
         <v>-6.9688409445004207E-2</v>
       </c>
       <c r="AB47" s="16" cm="1">
-        <f t="array" ref="AB47">SQRT(SUMPRODUCT(((J47:O47-P47:U47)/$AE$3:$AJ$3)^2)/6)*100</f>
+        <f t="array" ref="AB47">SQRT(SUMPRODUCT(((J47:O47-P47:U47)/$AL$3:$AQ$3)^2)/6)*100</f>
         <v>0.3516347834292794</v>
       </c>
-      <c r="AC47" s="5">
+      <c r="AC47" s="16"/>
+      <c r="AD47" s="16"/>
+      <c r="AE47" s="16"/>
+      <c r="AF47" s="16"/>
+      <c r="AG47" s="16"/>
+      <c r="AH47" s="16"/>
+      <c r="AI47" s="16"/>
+      <c r="AJ47" s="5">
         <f t="shared" si="7"/>
         <v>0.04</v>
       </c>
-      <c r="AD47" s="13">
+      <c r="AK47" s="13">
         <v>7282.9201268507204</v>
       </c>
     </row>
-    <row r="48" spans="1:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="17">
         <v>1.4313963908</v>
       </c>
@@ -6463,18 +6867,25 @@
         <v>-0.20027499895765244</v>
       </c>
       <c r="AB48" s="16" cm="1">
-        <f t="array" ref="AB48">SQRT(SUMPRODUCT(((J48:O48-P48:U48)/$AE$3:$AJ$3)^2)/6)*100</f>
+        <f t="array" ref="AB48">SQRT(SUMPRODUCT(((J48:O48-P48:U48)/$AL$3:$AQ$3)^2)/6)*100</f>
         <v>2.4933716951386957</v>
       </c>
-      <c r="AC48" s="5">
+      <c r="AC48" s="16"/>
+      <c r="AD48" s="16"/>
+      <c r="AE48" s="16"/>
+      <c r="AF48" s="16"/>
+      <c r="AG48" s="16"/>
+      <c r="AH48" s="16"/>
+      <c r="AI48" s="16"/>
+      <c r="AJ48" s="5">
         <f t="shared" si="7"/>
         <v>4.0000000000000008E-2</v>
       </c>
-      <c r="AD48" s="13">
+      <c r="AK48" s="13">
         <v>241115.288489914</v>
       </c>
     </row>
-    <row r="49" spans="1:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="17">
         <v>1.1008731407000001</v>
       </c>
@@ -6563,18 +6974,25 @@
         <v>1.1465328913826012E-2</v>
       </c>
       <c r="AB49" s="16" cm="1">
-        <f t="array" ref="AB49">SQRT(SUMPRODUCT(((J49:O49-P49:U49)/$AE$3:$AJ$3)^2)/6)*100</f>
+        <f t="array" ref="AB49">SQRT(SUMPRODUCT(((J49:O49-P49:U49)/$AL$3:$AQ$3)^2)/6)*100</f>
         <v>0.36108353148552325</v>
       </c>
-      <c r="AC49" s="5">
+      <c r="AC49" s="16"/>
+      <c r="AD49" s="16"/>
+      <c r="AE49" s="16"/>
+      <c r="AF49" s="16"/>
+      <c r="AG49" s="16"/>
+      <c r="AH49" s="16"/>
+      <c r="AI49" s="16"/>
+      <c r="AJ49" s="5">
         <f t="shared" si="7"/>
         <v>3.9999999999999994E-2</v>
       </c>
-      <c r="AD49" s="13">
+      <c r="AK49" s="13">
         <v>21611.028785295999</v>
       </c>
     </row>
-    <row r="50" spans="1:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="17">
         <v>1.1548404238000001</v>
       </c>
@@ -6663,18 +7081,25 @@
         <v>-6.9625617969803821E-2</v>
       </c>
       <c r="AB50" s="16" cm="1">
-        <f t="array" ref="AB50">SQRT(SUMPRODUCT(((J50:O50-P50:U50)/$AE$3:$AJ$3)^2)/6)*100</f>
+        <f t="array" ref="AB50">SQRT(SUMPRODUCT(((J50:O50-P50:U50)/$AL$3:$AQ$3)^2)/6)*100</f>
         <v>0.28114913535450997</v>
       </c>
-      <c r="AC50" s="5">
+      <c r="AC50" s="16"/>
+      <c r="AD50" s="16"/>
+      <c r="AE50" s="16"/>
+      <c r="AF50" s="16"/>
+      <c r="AG50" s="16"/>
+      <c r="AH50" s="16"/>
+      <c r="AI50" s="16"/>
+      <c r="AJ50" s="5">
         <f t="shared" si="7"/>
         <v>3.9999999999999994E-2</v>
       </c>
-      <c r="AD50" s="13">
+      <c r="AK50" s="13">
         <v>20365.130850537898</v>
       </c>
     </row>
-    <row r="51" spans="1:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="17">
         <v>1.1816252039999999</v>
       </c>
@@ -6763,18 +7188,25 @@
         <v>-5.4239450051109417E-2</v>
       </c>
       <c r="AB51" s="16" cm="1">
-        <f t="array" ref="AB51">SQRT(SUMPRODUCT(((J51:O51-P51:U51)/$AE$3:$AJ$3)^2)/6)*100</f>
+        <f t="array" ref="AB51">SQRT(SUMPRODUCT(((J51:O51-P51:U51)/$AL$3:$AQ$3)^2)/6)*100</f>
         <v>0.3635803025496448</v>
       </c>
-      <c r="AC51" s="5">
+      <c r="AC51" s="16"/>
+      <c r="AD51" s="16"/>
+      <c r="AE51" s="16"/>
+      <c r="AF51" s="16"/>
+      <c r="AG51" s="16"/>
+      <c r="AH51" s="16"/>
+      <c r="AI51" s="16"/>
+      <c r="AJ51" s="5">
         <f t="shared" si="7"/>
         <v>0.04</v>
       </c>
-      <c r="AD51" s="13">
+      <c r="AK51" s="13">
         <v>7124.2300644876796</v>
       </c>
     </row>
-    <row r="52" spans="1:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="17">
         <v>0.93729510640000002</v>
       </c>
@@ -6863,18 +7295,25 @@
         <v>-1.7758101463260512E-2</v>
       </c>
       <c r="AB52" s="16" cm="1">
-        <f t="array" ref="AB52">SQRT(SUMPRODUCT(((J52:O52-P52:U52)/$AE$3:$AJ$3)^2)/6)*100</f>
+        <f t="array" ref="AB52">SQRT(SUMPRODUCT(((J52:O52-P52:U52)/$AL$3:$AQ$3)^2)/6)*100</f>
         <v>0.42957288223014695</v>
       </c>
-      <c r="AC52" s="5">
+      <c r="AC52" s="16"/>
+      <c r="AD52" s="16"/>
+      <c r="AE52" s="16"/>
+      <c r="AF52" s="16"/>
+      <c r="AG52" s="16"/>
+      <c r="AH52" s="16"/>
+      <c r="AI52" s="16"/>
+      <c r="AJ52" s="5">
         <f t="shared" si="7"/>
         <v>4.0000000000000008E-2</v>
       </c>
-      <c r="AD52" s="13">
+      <c r="AK52" s="13">
         <v>4678.6265867306902</v>
       </c>
     </row>
-    <row r="53" spans="1:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="16">
         <v>0.32556561499999997</v>
       </c>
@@ -6918,11 +7357,11 @@
         <f>AVERAGE(V3:V52)</f>
         <v>-3.5313484647205045E-4</v>
       </c>
-      <c r="W53" s="5">
+      <c r="W53" s="11">
         <f t="shared" ref="W53:AA53" si="33">AVERAGE(W3:W52)</f>
         <v>-3.0225398327429385E-4</v>
       </c>
-      <c r="X53" s="5">
+      <c r="X53" s="11">
         <f t="shared" si="33"/>
         <v>8.3417181126393904E-4</v>
       </c>
@@ -6939,12 +7378,19 @@
         <v>-6.6286087627894482E-3</v>
       </c>
       <c r="AB53" s="16"/>
-      <c r="AC53" s="5"/>
-      <c r="AD53" s="13">
+      <c r="AC53" s="16"/>
+      <c r="AD53" s="16"/>
+      <c r="AE53" s="16"/>
+      <c r="AF53" s="16"/>
+      <c r="AG53" s="16"/>
+      <c r="AH53" s="16"/>
+      <c r="AI53" s="16"/>
+      <c r="AJ53" s="5"/>
+      <c r="AK53" s="13">
         <v>5678.4546433241303</v>
       </c>
     </row>
-    <row r="54" spans="1:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="16">
         <v>0.34779033799999998</v>
       </c>
@@ -6991,12 +7437,19 @@
       <c r="Z54" s="5"/>
       <c r="AA54" s="5"/>
       <c r="AB54" s="16"/>
-      <c r="AC54" s="5"/>
-      <c r="AD54" s="13">
+      <c r="AC54" s="16"/>
+      <c r="AD54" s="16"/>
+      <c r="AE54" s="16"/>
+      <c r="AF54" s="16"/>
+      <c r="AG54" s="16"/>
+      <c r="AH54" s="16"/>
+      <c r="AI54" s="16"/>
+      <c r="AJ54" s="5"/>
+      <c r="AK54" s="13">
         <v>5180.45334190619</v>
       </c>
     </row>
-    <row r="55" spans="1:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="16">
         <v>1.1244386973</v>
       </c>
@@ -7043,12 +7496,19 @@
       <c r="Z55" s="5"/>
       <c r="AA55" s="5"/>
       <c r="AB55" s="16"/>
-      <c r="AC55" s="5"/>
-      <c r="AD55" s="13">
+      <c r="AC55" s="16"/>
+      <c r="AD55" s="16"/>
+      <c r="AE55" s="16"/>
+      <c r="AF55" s="16"/>
+      <c r="AG55" s="16"/>
+      <c r="AH55" s="16"/>
+      <c r="AI55" s="16"/>
+      <c r="AJ55" s="5"/>
+      <c r="AK55" s="13">
         <v>5663.0654180951597</v>
       </c>
     </row>
-    <row r="56" spans="1:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="16">
         <v>0.87685121659999998</v>
       </c>
@@ -7095,12 +7555,19 @@
       <c r="Z56" s="5"/>
       <c r="AA56" s="5"/>
       <c r="AB56" s="16"/>
-      <c r="AC56" s="5"/>
-      <c r="AD56" s="13">
+      <c r="AC56" s="16"/>
+      <c r="AD56" s="16"/>
+      <c r="AE56" s="16"/>
+      <c r="AF56" s="16"/>
+      <c r="AG56" s="16"/>
+      <c r="AH56" s="16"/>
+      <c r="AI56" s="16"/>
+      <c r="AJ56" s="5"/>
+      <c r="AK56" s="13">
         <v>5078.30649569658</v>
       </c>
     </row>
-    <row r="57" spans="1:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="16">
         <v>0.59547924330000002</v>
       </c>
@@ -7147,12 +7614,19 @@
       <c r="Z57" s="5"/>
       <c r="AA57" s="5"/>
       <c r="AB57" s="16"/>
-      <c r="AC57" s="5"/>
-      <c r="AD57" s="13">
+      <c r="AC57" s="16"/>
+      <c r="AD57" s="16"/>
+      <c r="AE57" s="16"/>
+      <c r="AF57" s="16"/>
+      <c r="AG57" s="16"/>
+      <c r="AH57" s="16"/>
+      <c r="AI57" s="16"/>
+      <c r="AJ57" s="5"/>
+      <c r="AK57" s="13">
         <v>1157.89131373184</v>
       </c>
     </row>
-    <row r="58" spans="1:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="16">
         <v>1.3901836501</v>
       </c>
@@ -7199,12 +7673,19 @@
       <c r="Z58" s="5"/>
       <c r="AA58" s="5"/>
       <c r="AB58" s="16"/>
-      <c r="AC58" s="5"/>
-      <c r="AD58" s="13">
+      <c r="AC58" s="16"/>
+      <c r="AD58" s="16"/>
+      <c r="AE58" s="16"/>
+      <c r="AF58" s="16"/>
+      <c r="AG58" s="16"/>
+      <c r="AH58" s="16"/>
+      <c r="AI58" s="16"/>
+      <c r="AJ58" s="5"/>
+      <c r="AK58" s="13">
         <v>2905.0269528538001</v>
       </c>
     </row>
-    <row r="59" spans="1:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="16">
         <v>0.37261524629999998</v>
       </c>
@@ -7251,12 +7732,19 @@
       <c r="Z59" s="5"/>
       <c r="AA59" s="5"/>
       <c r="AB59" s="16"/>
-      <c r="AC59" s="5"/>
-      <c r="AD59" s="13">
+      <c r="AC59" s="16"/>
+      <c r="AD59" s="16"/>
+      <c r="AE59" s="16"/>
+      <c r="AF59" s="16"/>
+      <c r="AG59" s="16"/>
+      <c r="AH59" s="16"/>
+      <c r="AI59" s="16"/>
+      <c r="AJ59" s="5"/>
+      <c r="AK59" s="13">
         <v>847.08203095288104</v>
       </c>
     </row>
-    <row r="60" spans="1:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="16">
         <v>1.4531678181000001</v>
       </c>
@@ -7303,12 +7791,19 @@
       <c r="Z60" s="5"/>
       <c r="AA60" s="5"/>
       <c r="AB60" s="16"/>
-      <c r="AC60" s="5"/>
-      <c r="AD60" s="13">
+      <c r="AC60" s="16"/>
+      <c r="AD60" s="16"/>
+      <c r="AE60" s="16"/>
+      <c r="AF60" s="16"/>
+      <c r="AG60" s="16"/>
+      <c r="AH60" s="16"/>
+      <c r="AI60" s="16"/>
+      <c r="AJ60" s="5"/>
+      <c r="AK60" s="13">
         <v>5725.3440610789203</v>
       </c>
     </row>
-    <row r="61" spans="1:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="16">
         <v>0.36590931840000002</v>
       </c>
@@ -7355,12 +7850,19 @@
       <c r="Z61" s="5"/>
       <c r="AA61" s="5"/>
       <c r="AB61" s="16"/>
-      <c r="AC61" s="5"/>
-      <c r="AD61" s="13">
+      <c r="AC61" s="16"/>
+      <c r="AD61" s="16"/>
+      <c r="AE61" s="16"/>
+      <c r="AF61" s="16"/>
+      <c r="AG61" s="16"/>
+      <c r="AH61" s="16"/>
+      <c r="AI61" s="16"/>
+      <c r="AJ61" s="5"/>
+      <c r="AK61" s="13">
         <v>4839.09033436134</v>
       </c>
     </row>
-    <row r="62" spans="1:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="16">
         <v>0.71858942609999998</v>
       </c>
@@ -7407,19 +7909,30 @@
       <c r="Z62" s="5"/>
       <c r="AA62" s="5"/>
       <c r="AB62" s="16"/>
-      <c r="AC62" s="5"/>
-      <c r="AD62" s="13">
+      <c r="AC62" s="16"/>
+      <c r="AD62" s="16"/>
+      <c r="AE62" s="16"/>
+      <c r="AF62" s="16"/>
+      <c r="AG62" s="16"/>
+      <c r="AH62" s="16"/>
+      <c r="AI62" s="16"/>
+      <c r="AJ62" s="5"/>
+      <c r="AK62" s="13">
         <v>4286.1131822769203</v>
       </c>
+    </row>
+    <row r="117" spans="24:24" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="X117" s="45"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="AE1:AJ1"/>
+  <mergeCells count="7">
+    <mergeCell ref="AL1:AQ1"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="J1:O1"/>
     <mergeCell ref="P1:U1"/>
-    <mergeCell ref="AC1:AD1"/>
-    <mergeCell ref="V1:AB1"/>
+    <mergeCell ref="AJ1:AK1"/>
+    <mergeCell ref="V1:AA1"/>
+    <mergeCell ref="AB1:AI1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -7464,45 +7977,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="26" t="s">
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
-      <c r="O1" s="27"/>
-      <c r="P1" s="31" t="s">
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
+      <c r="P1" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="Q1" s="32"/>
-      <c r="R1" s="32"/>
-      <c r="S1" s="32"/>
-      <c r="T1" s="32"/>
-      <c r="U1" s="32"/>
-      <c r="V1" s="32"/>
-      <c r="W1" s="33" t="s">
+      <c r="Q1" s="30"/>
+      <c r="R1" s="30"/>
+      <c r="S1" s="30"/>
+      <c r="T1" s="30"/>
+      <c r="U1" s="30"/>
+      <c r="V1" s="30"/>
+      <c r="W1" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="X1" s="33"/>
-      <c r="Y1" s="33"/>
-      <c r="Z1" s="33"/>
-      <c r="AA1" s="33"/>
-      <c r="AB1" s="33"/>
-      <c r="AC1" s="33"/>
-      <c r="AD1" s="33"/>
-      <c r="AE1" s="33"/>
+      <c r="X1" s="31"/>
+      <c r="Y1" s="31"/>
+      <c r="Z1" s="31"/>
+      <c r="AA1" s="31"/>
+      <c r="AB1" s="31"/>
+      <c r="AC1" s="31"/>
+      <c r="AD1" s="31"/>
+      <c r="AE1" s="31"/>
       <c r="AF1" s="20" t="s">
         <v>31</v>
       </c>
@@ -7606,14 +8119,14 @@
       <c r="AE2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="AF2" s="34" t="s">
+      <c r="AF2" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="AG2" s="34"/>
-      <c r="AH2" s="34"/>
-      <c r="AI2" s="34"/>
-      <c r="AJ2" s="34"/>
-      <c r="AK2" s="34"/>
+      <c r="AG2" s="32"/>
+      <c r="AH2" s="32"/>
+      <c r="AI2" s="32"/>
+      <c r="AJ2" s="32"/>
+      <c r="AK2" s="32"/>
     </row>
     <row r="3" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
@@ -8013,14 +8526,14 @@
         <f t="shared" si="1"/>
         <v>1.2596068495192014E-3</v>
       </c>
-      <c r="AF5" s="35" t="s">
+      <c r="AF5" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="AG5" s="36"/>
-      <c r="AH5" s="36"/>
-      <c r="AI5" s="36"/>
-      <c r="AJ5" s="36"/>
-      <c r="AK5" s="36"/>
+      <c r="AG5" s="24"/>
+      <c r="AH5" s="24"/>
+      <c r="AI5" s="24"/>
+      <c r="AJ5" s="24"/>
+      <c r="AK5" s="24"/>
     </row>
     <row r="6" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
@@ -13717,45 +14230,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="26" t="s">
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
-      <c r="O1" s="27"/>
-      <c r="P1" s="31" t="s">
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
+      <c r="P1" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="Q1" s="32"/>
-      <c r="R1" s="32"/>
-      <c r="S1" s="32"/>
-      <c r="T1" s="32"/>
-      <c r="U1" s="32"/>
-      <c r="V1" s="32"/>
-      <c r="W1" s="33" t="s">
+      <c r="Q1" s="30"/>
+      <c r="R1" s="30"/>
+      <c r="S1" s="30"/>
+      <c r="T1" s="30"/>
+      <c r="U1" s="30"/>
+      <c r="V1" s="30"/>
+      <c r="W1" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="X1" s="33"/>
-      <c r="Y1" s="33"/>
-      <c r="Z1" s="33"/>
-      <c r="AA1" s="33"/>
-      <c r="AB1" s="33"/>
-      <c r="AC1" s="33"/>
-      <c r="AD1" s="33"/>
-      <c r="AE1" s="33"/>
+      <c r="X1" s="31"/>
+      <c r="Y1" s="31"/>
+      <c r="Z1" s="31"/>
+      <c r="AA1" s="31"/>
+      <c r="AB1" s="31"/>
+      <c r="AC1" s="31"/>
+      <c r="AD1" s="31"/>
+      <c r="AE1" s="31"/>
       <c r="AF1" s="20" t="s">
         <v>31</v>
       </c>
@@ -13859,14 +14372,14 @@
       <c r="AE2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="AF2" s="34" t="s">
+      <c r="AF2" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="AG2" s="34"/>
-      <c r="AH2" s="34"/>
-      <c r="AI2" s="34"/>
-      <c r="AJ2" s="34"/>
-      <c r="AK2" s="34"/>
+      <c r="AG2" s="32"/>
+      <c r="AH2" s="32"/>
+      <c r="AI2" s="32"/>
+      <c r="AJ2" s="32"/>
+      <c r="AK2" s="32"/>
     </row>
     <row r="3" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
@@ -14266,14 +14779,14 @@
         <f t="shared" si="1"/>
         <v>6.4451360756412335E-4</v>
       </c>
-      <c r="AF5" s="35" t="s">
+      <c r="AF5" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="AG5" s="36"/>
-      <c r="AH5" s="36"/>
-      <c r="AI5" s="36"/>
-      <c r="AJ5" s="36"/>
-      <c r="AK5" s="36"/>
+      <c r="AG5" s="24"/>
+      <c r="AH5" s="24"/>
+      <c r="AI5" s="24"/>
+      <c r="AJ5" s="24"/>
+      <c r="AK5" s="24"/>
     </row>
     <row r="6" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
@@ -14657,6 +15170,14 @@
       <c r="AE8" s="8">
         <f t="shared" si="1"/>
         <v>2.7136481380246602E-4</v>
+      </c>
+      <c r="AF8" s="12">
+        <f>MEDIAN(AC3:AC52)</f>
+        <v>0.14828344493926837</v>
+      </c>
+      <c r="AG8" s="12">
+        <f>MEDIAN(AD3:AD52)</f>
+        <v>1.0117485939609034E-2</v>
       </c>
     </row>
     <row r="9" spans="1:37" x14ac:dyDescent="0.25">
@@ -19958,45 +20479,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="26" t="s">
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
-      <c r="O1" s="27"/>
-      <c r="P1" s="31" t="s">
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
+      <c r="P1" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="Q1" s="32"/>
-      <c r="R1" s="32"/>
-      <c r="S1" s="32"/>
-      <c r="T1" s="32"/>
-      <c r="U1" s="32"/>
-      <c r="V1" s="32"/>
-      <c r="W1" s="33" t="s">
+      <c r="Q1" s="30"/>
+      <c r="R1" s="30"/>
+      <c r="S1" s="30"/>
+      <c r="T1" s="30"/>
+      <c r="U1" s="30"/>
+      <c r="V1" s="30"/>
+      <c r="W1" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="X1" s="33"/>
-      <c r="Y1" s="33"/>
-      <c r="Z1" s="33"/>
-      <c r="AA1" s="33"/>
-      <c r="AB1" s="33"/>
-      <c r="AC1" s="33"/>
-      <c r="AD1" s="33"/>
-      <c r="AE1" s="33"/>
+      <c r="X1" s="31"/>
+      <c r="Y1" s="31"/>
+      <c r="Z1" s="31"/>
+      <c r="AA1" s="31"/>
+      <c r="AB1" s="31"/>
+      <c r="AC1" s="31"/>
+      <c r="AD1" s="31"/>
+      <c r="AE1" s="31"/>
       <c r="AF1" s="20" t="s">
         <v>31</v>
       </c>
@@ -20100,14 +20621,14 @@
       <c r="AE2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="AF2" s="34" t="s">
+      <c r="AF2" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="AG2" s="34"/>
-      <c r="AH2" s="34"/>
-      <c r="AI2" s="34"/>
-      <c r="AJ2" s="34"/>
-      <c r="AK2" s="34"/>
+      <c r="AG2" s="32"/>
+      <c r="AH2" s="32"/>
+      <c r="AI2" s="32"/>
+      <c r="AJ2" s="32"/>
+      <c r="AK2" s="32"/>
     </row>
     <row r="3" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
@@ -20507,14 +21028,14 @@
         <f t="shared" si="1"/>
         <v>0.77878621042016904</v>
       </c>
-      <c r="AF5" s="35" t="s">
+      <c r="AF5" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="AG5" s="36"/>
-      <c r="AH5" s="36"/>
-      <c r="AI5" s="36"/>
-      <c r="AJ5" s="36"/>
-      <c r="AK5" s="36"/>
+      <c r="AG5" s="24"/>
+      <c r="AH5" s="24"/>
+      <c r="AI5" s="24"/>
+      <c r="AJ5" s="24"/>
+      <c r="AK5" s="24"/>
     </row>
     <row r="6" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
@@ -20898,6 +21419,14 @@
       <c r="AE8" s="8">
         <f t="shared" si="1"/>
         <v>0.35215757109703494</v>
+      </c>
+      <c r="AF8" s="12">
+        <f>MEDIAN(AC3:AC52)</f>
+        <v>4.5469562032180527E-2</v>
+      </c>
+      <c r="AG8" s="12">
+        <f>MEDIAN(AD3:AD52)</f>
+        <v>3.3837105501073918E-3</v>
       </c>
     </row>
     <row r="9" spans="1:37" x14ac:dyDescent="0.25">
@@ -26170,30 +26699,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="39"/>
-      <c r="H1" s="37" t="s">
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="38"/>
+      <c r="H1" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
-      <c r="K1" s="38"/>
-      <c r="L1" s="38"/>
-      <c r="M1" s="39"/>
-      <c r="O1" s="37" t="s">
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="38"/>
+      <c r="O1" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="P1" s="38"/>
-      <c r="Q1" s="38"/>
-      <c r="R1" s="38"/>
-      <c r="S1" s="38"/>
-      <c r="T1" s="39"/>
+      <c r="P1" s="37"/>
+      <c r="Q1" s="37"/>
+      <c r="R1" s="37"/>
+      <c r="S1" s="37"/>
+      <c r="T1" s="38"/>
     </row>
     <row r="2" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -27248,7 +27777,2676 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1DB4261-934D-41E3-BBC3-63975A38C41E}">
+  <dimension ref="D3:X52"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="3" spans="4:24" x14ac:dyDescent="0.25">
+      <c r="D3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0.57634630980000001</v>
+      </c>
+      <c r="F3" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0.78539999999999999</v>
+      </c>
+      <c r="H3" s="5">
+        <v>1.1398024601000001</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0.02</v>
+      </c>
+      <c r="J3" s="5">
+        <v>5.4977999999999998</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0.49272223679999999</v>
+      </c>
+      <c r="L3" s="5">
+        <v>4.4756011583999999</v>
+      </c>
+      <c r="M3" s="5">
+        <v>4.1915536561</v>
+      </c>
+      <c r="N3" t="s">
+        <v>44</v>
+      </c>
+      <c r="R3">
+        <v>0.3</v>
+      </c>
+      <c r="S3">
+        <v>0.2</v>
+      </c>
+      <c r="T3">
+        <v>1.2084999999999999</v>
+      </c>
+      <c r="U3">
+        <v>1.1049</v>
+      </c>
+      <c r="V3">
+        <v>6.83E-2</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>1.1999999999999999E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="4:24" x14ac:dyDescent="0.25">
+      <c r="E4" s="5">
+        <v>1.2961945501000001</v>
+      </c>
+      <c r="F4" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="G4" s="5">
+        <v>4.7123999999999997</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0.31907560010000002</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0.02</v>
+      </c>
+      <c r="J4" s="5">
+        <v>1.5708</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0.53253118440000002</v>
+      </c>
+      <c r="L4" s="5">
+        <v>1.6232893740000001</v>
+      </c>
+      <c r="M4" s="5">
+        <v>9.6932284100000002E-2</v>
+      </c>
+      <c r="N4" t="s">
+        <v>44</v>
+      </c>
+      <c r="R4">
+        <v>1.0255000000000001</v>
+      </c>
+      <c r="S4">
+        <v>0.2</v>
+      </c>
+      <c r="T4">
+        <v>4.9531999999999998</v>
+      </c>
+      <c r="U4">
+        <v>0.34689999999999999</v>
+      </c>
+      <c r="V4">
+        <v>0.2</v>
+      </c>
+      <c r="W4">
+        <v>3.9266999999999999</v>
+      </c>
+      <c r="X4">
+        <v>2.0000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="5" spans="4:24" x14ac:dyDescent="0.25">
+      <c r="E5" s="5">
+        <v>0.3432844504</v>
+      </c>
+      <c r="F5" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="G5" s="5">
+        <v>3.1415999999999999</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0.75633386430000005</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0.02</v>
+      </c>
+      <c r="J5" s="5">
+        <v>3.1415999999999999</v>
+      </c>
+      <c r="K5" s="5">
+        <v>3.5593988404000001</v>
+      </c>
+      <c r="L5" s="5">
+        <v>2.6173593599</v>
+      </c>
+      <c r="M5" s="5">
+        <v>2.7214845023000001</v>
+      </c>
+      <c r="N5" t="s">
+        <v>44</v>
+      </c>
+      <c r="R5">
+        <v>0.42880000000000001</v>
+      </c>
+      <c r="S5">
+        <v>0.16139999999999999</v>
+      </c>
+      <c r="T5">
+        <v>3.1427999999999998</v>
+      </c>
+      <c r="U5">
+        <v>0.66930000000000001</v>
+      </c>
+      <c r="V5">
+        <v>2.01E-2</v>
+      </c>
+      <c r="W5">
+        <v>3.1425000000000001</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="4:24" x14ac:dyDescent="0.25">
+      <c r="E6" s="5">
+        <v>0.83277602429999997</v>
+      </c>
+      <c r="F6" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="G6" s="5">
+        <v>4.7123999999999997</v>
+      </c>
+      <c r="H6" s="5">
+        <v>1.4193655153</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0.04</v>
+      </c>
+      <c r="J6" s="5">
+        <v>5.4977999999999998</v>
+      </c>
+      <c r="K6" s="5">
+        <v>4.2084858911999996</v>
+      </c>
+      <c r="L6" s="5">
+        <v>0.52916698419999997</v>
+      </c>
+      <c r="M6" s="5">
+        <v>2.5150427606000001</v>
+      </c>
+      <c r="N6" t="s">
+        <v>44</v>
+      </c>
+      <c r="R6">
+        <v>0.83850000000000002</v>
+      </c>
+      <c r="S6">
+        <v>0.19819999999999999</v>
+      </c>
+      <c r="T6">
+        <v>4.7122000000000002</v>
+      </c>
+      <c r="U6">
+        <v>1.4148000000000001</v>
+      </c>
+      <c r="V6">
+        <v>3.9899999999999998E-2</v>
+      </c>
+      <c r="W6">
+        <v>5.5007999999999999</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="4:24" x14ac:dyDescent="0.25">
+      <c r="E7" s="5">
+        <v>0.3898403909</v>
+      </c>
+      <c r="F7" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="G7" s="5">
+        <v>1.5708</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0.45028828840000001</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0.04</v>
+      </c>
+      <c r="J7" s="5">
+        <v>2.3561999999999999</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0.34676129480000001</v>
+      </c>
+      <c r="L7" s="5">
+        <v>0.93612470940000003</v>
+      </c>
+      <c r="M7" s="5">
+        <v>2.0702513480000002</v>
+      </c>
+      <c r="R7">
+        <v>0.55279999999999996</v>
+      </c>
+      <c r="S7">
+        <v>0.14510000000000001</v>
+      </c>
+      <c r="T7">
+        <v>1.4137</v>
+      </c>
+      <c r="U7">
+        <v>0.43390000000000001</v>
+      </c>
+      <c r="V7">
+        <v>6.2399999999999997E-2</v>
+      </c>
+      <c r="W7">
+        <v>2.7677</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="4:24" x14ac:dyDescent="0.25">
+      <c r="E8">
+        <v>0.86958752539999995</v>
+      </c>
+      <c r="F8">
+        <v>0.2</v>
+      </c>
+      <c r="G8">
+        <v>0.78539999999999999</v>
+      </c>
+      <c r="H8">
+        <v>0.66933871</v>
+      </c>
+      <c r="I8">
+        <v>0.04</v>
+      </c>
+      <c r="J8">
+        <v>0.78539999999999999</v>
+      </c>
+      <c r="K8">
+        <v>2.0486073985000002</v>
+      </c>
+      <c r="L8">
+        <v>1.4427408886999999</v>
+      </c>
+      <c r="M8">
+        <v>0.53737298850000004</v>
+      </c>
+      <c r="N8" t="s">
+        <v>44</v>
+      </c>
+      <c r="R8">
+        <v>0.88849999999999996</v>
+      </c>
+      <c r="S8">
+        <v>0.19620000000000001</v>
+      </c>
+      <c r="T8">
+        <v>0.78539999999999999</v>
+      </c>
+      <c r="U8">
+        <v>0.65169999999999995</v>
+      </c>
+      <c r="V8">
+        <v>3.8600000000000002E-2</v>
+      </c>
+      <c r="W8">
+        <v>0.78590000000000004</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="4:24" x14ac:dyDescent="0.25">
+      <c r="E9">
+        <v>1.2260241731999999</v>
+      </c>
+      <c r="F9">
+        <v>0.2</v>
+      </c>
+      <c r="G9">
+        <v>3.1415999999999999</v>
+      </c>
+      <c r="H9">
+        <v>0.53124592000000004</v>
+      </c>
+      <c r="I9">
+        <v>0.04</v>
+      </c>
+      <c r="J9">
+        <v>1.5708</v>
+      </c>
+      <c r="K9">
+        <v>2.1721905802000001</v>
+      </c>
+      <c r="L9">
+        <v>4.8592739976999999</v>
+      </c>
+      <c r="M9">
+        <v>4.1505258277000001</v>
+      </c>
+      <c r="N9" t="s">
+        <v>44</v>
+      </c>
+      <c r="R9">
+        <v>1.226</v>
+      </c>
+      <c r="S9">
+        <v>0.2</v>
+      </c>
+      <c r="T9">
+        <v>3.1421000000000001</v>
+      </c>
+      <c r="U9">
+        <v>0.53169999999999995</v>
+      </c>
+      <c r="V9">
+        <v>4.02E-2</v>
+      </c>
+      <c r="W9">
+        <v>1.5707</v>
+      </c>
+      <c r="X9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="4:24" x14ac:dyDescent="0.25">
+      <c r="E10">
+        <v>1.4922792275000001</v>
+      </c>
+      <c r="F10">
+        <v>0.2</v>
+      </c>
+      <c r="G10">
+        <v>2.3561999999999999</v>
+      </c>
+      <c r="H10">
+        <v>1.2493008810999999</v>
+      </c>
+      <c r="I10">
+        <v>0.04</v>
+      </c>
+      <c r="J10">
+        <v>0.78539999999999999</v>
+      </c>
+      <c r="K10">
+        <v>0.65138204079999995</v>
+      </c>
+      <c r="L10">
+        <v>2.3960292019999998</v>
+      </c>
+      <c r="M10">
+        <v>3.8310385232000002</v>
+      </c>
+      <c r="N10" t="s">
+        <v>44</v>
+      </c>
+      <c r="R10">
+        <v>1.4927999999999999</v>
+      </c>
+      <c r="S10">
+        <v>0.19950000000000001</v>
+      </c>
+      <c r="T10">
+        <v>2.3696999999999999</v>
+      </c>
+      <c r="U10">
+        <v>1.2652000000000001</v>
+      </c>
+      <c r="V10">
+        <v>4.24E-2</v>
+      </c>
+      <c r="W10">
+        <v>0.78400000000000003</v>
+      </c>
+      <c r="X10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="4:24" x14ac:dyDescent="0.25">
+      <c r="E11">
+        <v>1.4258680059</v>
+      </c>
+      <c r="F11">
+        <v>0.2</v>
+      </c>
+      <c r="G11">
+        <v>4.7123999999999997</v>
+      </c>
+      <c r="H11">
+        <v>0.35291314260000001</v>
+      </c>
+      <c r="I11">
+        <v>0.04</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>3.4810259851000001</v>
+      </c>
+      <c r="L11">
+        <v>1.1294030872</v>
+      </c>
+      <c r="M11">
+        <v>4.9138255752999997</v>
+      </c>
+      <c r="N11" t="s">
+        <v>44</v>
+      </c>
+      <c r="R11">
+        <v>1.4948999999999999</v>
+      </c>
+      <c r="S11">
+        <v>0.19889999999999999</v>
+      </c>
+      <c r="T11">
+        <v>4.3463000000000003</v>
+      </c>
+      <c r="U11">
+        <v>0.81730000000000003</v>
+      </c>
+      <c r="V11">
+        <v>0.14360000000000001</v>
+      </c>
+      <c r="W11">
+        <v>6.2831999999999999</v>
+      </c>
+      <c r="X11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="4:24" x14ac:dyDescent="0.25">
+      <c r="E12">
+        <v>1.2847663906</v>
+      </c>
+      <c r="F12">
+        <v>0.18</v>
+      </c>
+      <c r="G12">
+        <v>0.78539999999999999</v>
+      </c>
+      <c r="H12">
+        <v>0.98965387010000005</v>
+      </c>
+      <c r="I12">
+        <v>0.04</v>
+      </c>
+      <c r="J12">
+        <v>3.927</v>
+      </c>
+      <c r="K12">
+        <v>3.2068327339999998</v>
+      </c>
+      <c r="L12">
+        <v>3.5469168124000001</v>
+      </c>
+      <c r="M12">
+        <v>1.1514404992</v>
+      </c>
+      <c r="N12" t="s">
+        <v>44</v>
+      </c>
+      <c r="R12">
+        <v>0.59899999999999998</v>
+      </c>
+      <c r="S12">
+        <v>0.2</v>
+      </c>
+      <c r="T12">
+        <v>1.3416999999999999</v>
+      </c>
+      <c r="U12">
+        <v>0.51849999999999996</v>
+      </c>
+      <c r="V12">
+        <v>0.2</v>
+      </c>
+      <c r="W12">
+        <v>9.9400000000000002E-2</v>
+      </c>
+      <c r="X12">
+        <v>1.2999999999999999E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="4:24" x14ac:dyDescent="0.25">
+      <c r="E13">
+        <v>0.82078888689999996</v>
+      </c>
+      <c r="F13">
+        <v>0.18</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>1.3252826163</v>
+      </c>
+      <c r="I13">
+        <v>0.04</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>3.9081993600000003E-2</v>
+      </c>
+      <c r="L13">
+        <v>2.9262884955000001</v>
+      </c>
+      <c r="M13">
+        <v>4.7431789933999999</v>
+      </c>
+      <c r="N13" t="s">
+        <v>44</v>
+      </c>
+      <c r="R13">
+        <v>0.8427</v>
+      </c>
+      <c r="S13">
+        <v>0.17780000000000001</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>1.3037000000000001</v>
+      </c>
+      <c r="V13">
+        <v>3.8800000000000001E-2</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="4:24" x14ac:dyDescent="0.25">
+      <c r="E14">
+        <v>0.51355824630000002</v>
+      </c>
+      <c r="F14">
+        <v>0.2</v>
+      </c>
+      <c r="G14">
+        <v>2.3561999999999999</v>
+      </c>
+      <c r="H14">
+        <v>0.96095190770000005</v>
+      </c>
+      <c r="I14">
+        <v>0.06</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>2.4382389278000001</v>
+      </c>
+      <c r="L14">
+        <v>4.2854047354000002</v>
+      </c>
+      <c r="M14">
+        <v>0.33901404839999999</v>
+      </c>
+      <c r="N14" t="s">
+        <v>44</v>
+      </c>
+      <c r="R14">
+        <v>0.5071</v>
+      </c>
+      <c r="S14">
+        <v>0.2</v>
+      </c>
+      <c r="T14">
+        <v>2.3451</v>
+      </c>
+      <c r="U14">
+        <v>0.95320000000000005</v>
+      </c>
+      <c r="V14">
+        <v>5.8700000000000002E-2</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="4:24" x14ac:dyDescent="0.25">
+      <c r="E15">
+        <v>0.35944564579999999</v>
+      </c>
+      <c r="F15">
+        <v>0.18</v>
+      </c>
+      <c r="G15">
+        <v>5.4977999999999998</v>
+      </c>
+      <c r="H15">
+        <v>1.2877652723999999</v>
+      </c>
+      <c r="I15">
+        <v>0.04</v>
+      </c>
+      <c r="J15">
+        <v>2.3561999999999999</v>
+      </c>
+      <c r="K15">
+        <v>2.1189458146</v>
+      </c>
+      <c r="L15">
+        <v>2.2606748846000002</v>
+      </c>
+      <c r="M15">
+        <v>0.94750633689999997</v>
+      </c>
+      <c r="N15" t="s">
+        <v>44</v>
+      </c>
+      <c r="R15">
+        <v>0.30270000000000002</v>
+      </c>
+      <c r="S15">
+        <v>0.02</v>
+      </c>
+      <c r="T15">
+        <v>3.3092000000000001</v>
+      </c>
+      <c r="U15">
+        <v>0.58979999999999999</v>
+      </c>
+      <c r="V15">
+        <v>0.02</v>
+      </c>
+      <c r="W15">
+        <v>1.9259999999999999</v>
+      </c>
+      <c r="X15">
+        <v>8.9999999999999998E-4</v>
+      </c>
+    </row>
+    <row r="16" spans="4:24" x14ac:dyDescent="0.25">
+      <c r="E16">
+        <v>1.2267525763</v>
+      </c>
+      <c r="F16">
+        <v>0.16</v>
+      </c>
+      <c r="G16">
+        <v>5.4977999999999998</v>
+      </c>
+      <c r="H16">
+        <v>1.4944716747</v>
+      </c>
+      <c r="I16">
+        <v>0.04</v>
+      </c>
+      <c r="J16">
+        <v>3.927</v>
+      </c>
+      <c r="K16">
+        <v>0.31884207939999998</v>
+      </c>
+      <c r="L16">
+        <v>3.8007215218999999</v>
+      </c>
+      <c r="M16">
+        <v>0.48541647729999998</v>
+      </c>
+      <c r="N16" t="s">
+        <v>44</v>
+      </c>
+      <c r="R16">
+        <v>1.296</v>
+      </c>
+      <c r="S16">
+        <v>0.15409999999999999</v>
+      </c>
+      <c r="T16">
+        <v>5.3589000000000002</v>
+      </c>
+      <c r="U16">
+        <v>1.3198000000000001</v>
+      </c>
+      <c r="V16">
+        <v>2.47E-2</v>
+      </c>
+      <c r="W16">
+        <v>3.8816000000000002</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="5:24" x14ac:dyDescent="0.25">
+      <c r="E17">
+        <v>0.64421489080000005</v>
+      </c>
+      <c r="F17">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0.8523470823</v>
+      </c>
+      <c r="I17">
+        <v>0.02</v>
+      </c>
+      <c r="J17">
+        <v>4.7123999999999997</v>
+      </c>
+      <c r="K17">
+        <v>8.0437148799999997E-2</v>
+      </c>
+      <c r="L17">
+        <v>0.35167971240000001</v>
+      </c>
+      <c r="M17">
+        <v>1.0501461195999999</v>
+      </c>
+      <c r="N17" t="s">
+        <v>44</v>
+      </c>
+      <c r="R17">
+        <v>0.3503</v>
+      </c>
+      <c r="S17">
+        <v>0.13689999999999999</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>0.30630000000000002</v>
+      </c>
+      <c r="V17">
+        <v>0.1368</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>2.0999999999999999E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="5:24" x14ac:dyDescent="0.25">
+      <c r="E18">
+        <v>1.1302547975999999</v>
+      </c>
+      <c r="F18">
+        <v>0.16</v>
+      </c>
+      <c r="G18">
+        <v>4.7123999999999997</v>
+      </c>
+      <c r="H18">
+        <v>1.3446433494000001</v>
+      </c>
+      <c r="I18">
+        <v>0.04</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>1.0644222964000001</v>
+      </c>
+      <c r="L18">
+        <v>1.4761094460999999</v>
+      </c>
+      <c r="M18">
+        <v>3.5278441351000001</v>
+      </c>
+      <c r="N18" t="s">
+        <v>44</v>
+      </c>
+      <c r="R18">
+        <v>1.1680999999999999</v>
+      </c>
+      <c r="S18">
+        <v>0.15609999999999999</v>
+      </c>
+      <c r="T18">
+        <v>4.7001999999999997</v>
+      </c>
+      <c r="U18">
+        <v>1.3580000000000001</v>
+      </c>
+      <c r="V18">
+        <v>4.1200000000000001E-2</v>
+      </c>
+      <c r="W18">
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="X18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="5:24" x14ac:dyDescent="0.25">
+      <c r="E19">
+        <v>0.44052297210000002</v>
+      </c>
+      <c r="F19">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="G19">
+        <v>0.78539999999999999</v>
+      </c>
+      <c r="H19">
+        <v>1.0539703866000001</v>
+      </c>
+      <c r="I19">
+        <v>0.02</v>
+      </c>
+      <c r="J19">
+        <v>3.1415999999999999</v>
+      </c>
+      <c r="K19">
+        <v>2.7027230284999999</v>
+      </c>
+      <c r="L19">
+        <v>1.6080541686000001</v>
+      </c>
+      <c r="M19">
+        <v>1.7094513416999999</v>
+      </c>
+      <c r="N19" t="s">
+        <v>44</v>
+      </c>
+      <c r="R19">
+        <v>0.48080000000000001</v>
+      </c>
+      <c r="S19">
+        <v>0.13120000000000001</v>
+      </c>
+      <c r="T19">
+        <v>0.77590000000000003</v>
+      </c>
+      <c r="U19">
+        <v>1.0862000000000001</v>
+      </c>
+      <c r="V19">
+        <v>2.07E-2</v>
+      </c>
+      <c r="W19">
+        <v>3.1650999999999998</v>
+      </c>
+      <c r="X19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="5:24" x14ac:dyDescent="0.25">
+      <c r="E20">
+        <v>1.4424756030000001</v>
+      </c>
+      <c r="F20">
+        <v>0.16</v>
+      </c>
+      <c r="G20">
+        <v>0.78539999999999999</v>
+      </c>
+      <c r="H20">
+        <v>1.1597422298</v>
+      </c>
+      <c r="I20">
+        <v>0.04</v>
+      </c>
+      <c r="J20">
+        <v>2.3561999999999999</v>
+      </c>
+      <c r="K20">
+        <v>4.8092587324</v>
+      </c>
+      <c r="L20">
+        <v>0.4784433911</v>
+      </c>
+      <c r="M20">
+        <v>4.3446054411999997</v>
+      </c>
+      <c r="N20" t="s">
+        <v>44</v>
+      </c>
+      <c r="R20">
+        <v>1.4424999999999999</v>
+      </c>
+      <c r="S20">
+        <v>0.16</v>
+      </c>
+      <c r="T20">
+        <v>0.78549999999999998</v>
+      </c>
+      <c r="U20">
+        <v>1.1596</v>
+      </c>
+      <c r="V20">
+        <v>0.04</v>
+      </c>
+      <c r="W20">
+        <v>2.3561999999999999</v>
+      </c>
+      <c r="X20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="5:24" x14ac:dyDescent="0.25">
+      <c r="E21">
+        <v>1.3085202701</v>
+      </c>
+      <c r="F21">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="G21">
+        <v>3.927</v>
+      </c>
+      <c r="H21">
+        <v>1.4295469448</v>
+      </c>
+      <c r="I21">
+        <v>0.02</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>4.5210753759999998</v>
+      </c>
+      <c r="L21">
+        <v>3.0172330613999998</v>
+      </c>
+      <c r="M21">
+        <v>0.83361274470000002</v>
+      </c>
+      <c r="N21" t="s">
+        <v>44</v>
+      </c>
+      <c r="R21">
+        <v>0.99970000000000003</v>
+      </c>
+      <c r="S21">
+        <v>0.17799999999999999</v>
+      </c>
+      <c r="T21">
+        <v>3.9245999999999999</v>
+      </c>
+      <c r="U21">
+        <v>1.2215</v>
+      </c>
+      <c r="V21">
+        <v>0.02</v>
+      </c>
+      <c r="W21">
+        <v>6.0923999999999996</v>
+      </c>
+      <c r="X21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="5:24" x14ac:dyDescent="0.25">
+      <c r="E22">
+        <v>1.0278031490999999</v>
+      </c>
+      <c r="F22">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0.3286386073</v>
+      </c>
+      <c r="I22">
+        <v>0.04</v>
+      </c>
+      <c r="J22">
+        <v>2.3561999999999999</v>
+      </c>
+      <c r="K22">
+        <v>2.4776605121999999</v>
+      </c>
+      <c r="L22">
+        <v>0.70416387319999996</v>
+      </c>
+      <c r="M22">
+        <v>1.306033752</v>
+      </c>
+      <c r="N22" t="s">
+        <v>44</v>
+      </c>
+      <c r="R22">
+        <v>0.65959999999999996</v>
+      </c>
+      <c r="S22">
+        <v>0.2</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0.3</v>
+      </c>
+      <c r="V22">
+        <v>3.6200000000000003E-2</v>
+      </c>
+      <c r="W22">
+        <v>0.96460000000000001</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="5:24" x14ac:dyDescent="0.25">
+      <c r="E23">
+        <v>0.8908774062</v>
+      </c>
+      <c r="F23">
+        <v>0.18</v>
+      </c>
+      <c r="G23">
+        <v>3.1415999999999999</v>
+      </c>
+      <c r="H23">
+        <v>0.88440675189999995</v>
+      </c>
+      <c r="I23">
+        <v>0.08</v>
+      </c>
+      <c r="J23">
+        <v>3.927</v>
+      </c>
+      <c r="K23">
+        <v>0.48462861940000002</v>
+      </c>
+      <c r="L23">
+        <v>1.6897568487000001</v>
+      </c>
+      <c r="M23">
+        <v>3.1701200912999998</v>
+      </c>
+      <c r="N23" t="s">
+        <v>44</v>
+      </c>
+      <c r="R23">
+        <v>0.99890000000000001</v>
+      </c>
+      <c r="S23">
+        <v>0.16739999999999999</v>
+      </c>
+      <c r="T23">
+        <v>3.1208999999999998</v>
+      </c>
+      <c r="U23">
+        <v>0.82740000000000002</v>
+      </c>
+      <c r="V23">
+        <v>8.2799999999999999E-2</v>
+      </c>
+      <c r="W23">
+        <v>4.0391000000000004</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="5:24" x14ac:dyDescent="0.25">
+      <c r="E24">
+        <v>1.2597568109999999</v>
+      </c>
+      <c r="F24">
+        <v>0.16</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0.58841219170000003</v>
+      </c>
+      <c r="I24">
+        <v>0.06</v>
+      </c>
+      <c r="J24">
+        <v>5.4977999999999998</v>
+      </c>
+      <c r="K24">
+        <v>3.9855186287</v>
+      </c>
+      <c r="L24">
+        <v>1.0426876676000001</v>
+      </c>
+      <c r="M24">
+        <v>0.31561411</v>
+      </c>
+      <c r="N24" t="s">
+        <v>44</v>
+      </c>
+      <c r="R24">
+        <v>0.8347</v>
+      </c>
+      <c r="S24">
+        <v>0.14560000000000001</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>0.76249999999999996</v>
+      </c>
+      <c r="V24">
+        <v>0.1381</v>
+      </c>
+      <c r="W24">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>1.1000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="25" spans="5:24" x14ac:dyDescent="0.25">
+      <c r="E25">
+        <v>0.65858340790000003</v>
+      </c>
+      <c r="F25">
+        <v>0.18</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0.498698221</v>
+      </c>
+      <c r="I25">
+        <v>0.08</v>
+      </c>
+      <c r="J25">
+        <v>0.78539999999999999</v>
+      </c>
+      <c r="K25">
+        <v>4.9301628920000002</v>
+      </c>
+      <c r="L25">
+        <v>1.8520278541999999</v>
+      </c>
+      <c r="M25">
+        <v>4.6646910371999999</v>
+      </c>
+      <c r="N25" t="s">
+        <v>44</v>
+      </c>
+      <c r="R25">
+        <v>0.67459999999999998</v>
+      </c>
+      <c r="S25">
+        <v>0.17849999999999999</v>
+      </c>
+      <c r="T25">
+        <v>1.14E-2</v>
+      </c>
+      <c r="U25">
+        <v>0.4824</v>
+      </c>
+      <c r="V25">
+        <v>7.7799999999999994E-2</v>
+      </c>
+      <c r="W25">
+        <v>0.79730000000000001</v>
+      </c>
+      <c r="X25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="5:24" x14ac:dyDescent="0.25">
+      <c r="E26">
+        <v>0.55032038400000005</v>
+      </c>
+      <c r="F26">
+        <v>0.16</v>
+      </c>
+      <c r="G26">
+        <v>3.1415999999999999</v>
+      </c>
+      <c r="H26">
+        <v>1.4487418581</v>
+      </c>
+      <c r="I26">
+        <v>0.08</v>
+      </c>
+      <c r="J26">
+        <v>2.3561999999999999</v>
+      </c>
+      <c r="K26">
+        <v>4.7175867132000002</v>
+      </c>
+      <c r="L26">
+        <v>1.3012665307</v>
+      </c>
+      <c r="M26">
+        <v>3.3668845907999998</v>
+      </c>
+      <c r="N26" t="s">
+        <v>44</v>
+      </c>
+      <c r="R26">
+        <v>0.86550000000000005</v>
+      </c>
+      <c r="S26">
+        <v>0.13150000000000001</v>
+      </c>
+      <c r="T26">
+        <v>3.1225000000000001</v>
+      </c>
+      <c r="U26">
+        <v>1.2327999999999999</v>
+      </c>
+      <c r="V26">
+        <v>7.9200000000000007E-2</v>
+      </c>
+      <c r="W26">
+        <v>2.1833</v>
+      </c>
+      <c r="X26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="5:24" x14ac:dyDescent="0.25">
+      <c r="E27">
+        <v>1.2531062278</v>
+      </c>
+      <c r="F27">
+        <v>0.18</v>
+      </c>
+      <c r="G27">
+        <v>5.4977999999999998</v>
+      </c>
+      <c r="H27">
+        <v>0.4702401397</v>
+      </c>
+      <c r="I27">
+        <v>0.1</v>
+      </c>
+      <c r="J27">
+        <v>5.4977999999999998</v>
+      </c>
+      <c r="K27">
+        <v>0.1483911762</v>
+      </c>
+      <c r="L27">
+        <v>0.2167359935</v>
+      </c>
+      <c r="M27">
+        <v>4.9349358513999997</v>
+      </c>
+      <c r="N27" t="s">
+        <v>44</v>
+      </c>
+      <c r="R27">
+        <v>1.0814999999999999</v>
+      </c>
+      <c r="S27">
+        <v>0.15939999999999999</v>
+      </c>
+      <c r="T27">
+        <v>4.6600000000000003E-2</v>
+      </c>
+      <c r="U27">
+        <v>1.2985</v>
+      </c>
+      <c r="V27">
+        <v>0.15620000000000001</v>
+      </c>
+      <c r="W27">
+        <v>4.8163</v>
+      </c>
+      <c r="X27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="5:24" x14ac:dyDescent="0.25">
+      <c r="E28">
+        <v>0.37674236639999997</v>
+      </c>
+      <c r="F28">
+        <v>0.12</v>
+      </c>
+      <c r="G28">
+        <v>5.4977999999999998</v>
+      </c>
+      <c r="H28">
+        <v>0.55884916829999998</v>
+      </c>
+      <c r="I28">
+        <v>0.04</v>
+      </c>
+      <c r="J28">
+        <v>5.4977999999999998</v>
+      </c>
+      <c r="K28">
+        <v>2.7463764360999998</v>
+      </c>
+      <c r="L28">
+        <v>4.0783358151</v>
+      </c>
+      <c r="M28">
+        <v>2.4827351898000001</v>
+      </c>
+      <c r="N28" t="s">
+        <v>44</v>
+      </c>
+      <c r="R28">
+        <v>0.80630000000000002</v>
+      </c>
+      <c r="S28">
+        <v>7.2599999999999998E-2</v>
+      </c>
+      <c r="T28">
+        <v>4.9812000000000003</v>
+      </c>
+      <c r="U28">
+        <v>0.4622</v>
+      </c>
+      <c r="V28">
+        <v>7.2599999999999998E-2</v>
+      </c>
+      <c r="W28">
+        <v>0.25330000000000003</v>
+      </c>
+      <c r="X28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="5:24" x14ac:dyDescent="0.25">
+      <c r="E29">
+        <v>0.99744538530000004</v>
+      </c>
+      <c r="F29">
+        <v>0.12</v>
+      </c>
+      <c r="G29">
+        <v>2.3561999999999999</v>
+      </c>
+      <c r="H29">
+        <v>0.63256510880000005</v>
+      </c>
+      <c r="I29">
+        <v>0.04</v>
+      </c>
+      <c r="J29">
+        <v>4.7123999999999997</v>
+      </c>
+      <c r="K29">
+        <v>1.0163068775999999</v>
+      </c>
+      <c r="L29">
+        <v>2.5468444695999999</v>
+      </c>
+      <c r="M29">
+        <v>0.1214735909</v>
+      </c>
+      <c r="N29" t="s">
+        <v>44</v>
+      </c>
+      <c r="R29">
+        <v>0.51719999999999999</v>
+      </c>
+      <c r="S29">
+        <v>0.1996</v>
+      </c>
+      <c r="T29">
+        <v>2.0973999999999999</v>
+      </c>
+      <c r="U29">
+        <v>0.57530000000000003</v>
+      </c>
+      <c r="V29">
+        <v>7.5899999999999995E-2</v>
+      </c>
+      <c r="W29">
+        <v>3.7867999999999999</v>
+      </c>
+      <c r="X29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="5:24" x14ac:dyDescent="0.25">
+      <c r="E30">
+        <v>0.91958396450000002</v>
+      </c>
+      <c r="F30">
+        <v>0.18</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>1.2327944816</v>
+      </c>
+      <c r="I30">
+        <v>0.1</v>
+      </c>
+      <c r="J30">
+        <v>4.7123999999999997</v>
+      </c>
+      <c r="K30">
+        <v>3.7350994551999999</v>
+      </c>
+      <c r="L30">
+        <v>0.10989542820000001</v>
+      </c>
+      <c r="M30">
+        <v>4.0041016991999996</v>
+      </c>
+      <c r="N30" t="s">
+        <v>44</v>
+      </c>
+      <c r="R30">
+        <v>0.95289999999999997</v>
+      </c>
+      <c r="S30">
+        <v>0.17710000000000001</v>
+      </c>
+      <c r="T30">
+        <v>5.9499999999999997E-2</v>
+      </c>
+      <c r="U30">
+        <v>1.2882</v>
+      </c>
+      <c r="V30">
+        <v>0.1038</v>
+      </c>
+      <c r="W30">
+        <v>4.6859999999999999</v>
+      </c>
+      <c r="X30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="5:24" x14ac:dyDescent="0.25">
+      <c r="E31">
+        <v>0.76015027209999997</v>
+      </c>
+      <c r="F31">
+        <v>0.18</v>
+      </c>
+      <c r="G31">
+        <v>2.3561999999999999</v>
+      </c>
+      <c r="H31">
+        <v>0.80034279419999999</v>
+      </c>
+      <c r="I31">
+        <v>0.1</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>4.7396783878999997</v>
+      </c>
+      <c r="L31">
+        <v>4.9071061610999998</v>
+      </c>
+      <c r="M31">
+        <v>1.8713340661</v>
+      </c>
+      <c r="N31" t="s">
+        <v>44</v>
+      </c>
+      <c r="R31">
+        <v>0.73929999999999996</v>
+      </c>
+      <c r="S31">
+        <v>0.18240000000000001</v>
+      </c>
+      <c r="T31">
+        <v>2.3529</v>
+      </c>
+      <c r="U31">
+        <v>0.78400000000000003</v>
+      </c>
+      <c r="V31">
+        <v>9.9599999999999994E-2</v>
+      </c>
+      <c r="W31">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="X31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="5:24" x14ac:dyDescent="0.25">
+      <c r="E32">
+        <v>0.9040684336</v>
+      </c>
+      <c r="F32">
+        <v>0.1</v>
+      </c>
+      <c r="G32">
+        <v>5.4977999999999998</v>
+      </c>
+      <c r="H32">
+        <v>0.68590239919999996</v>
+      </c>
+      <c r="I32">
+        <v>0.02</v>
+      </c>
+      <c r="J32">
+        <v>4.7123999999999997</v>
+      </c>
+      <c r="K32">
+        <v>3.1050919126999998</v>
+      </c>
+      <c r="L32">
+        <v>4.9790166179000002</v>
+      </c>
+      <c r="M32">
+        <v>4.7088396990000003</v>
+      </c>
+      <c r="N32" t="s">
+        <v>44</v>
+      </c>
+      <c r="R32">
+        <v>0.36759999999999998</v>
+      </c>
+      <c r="S32">
+        <v>0.13059999999999999</v>
+      </c>
+      <c r="T32">
+        <v>1E-4</v>
+      </c>
+      <c r="U32">
+        <v>1.3512999999999999</v>
+      </c>
+      <c r="V32">
+        <v>5.8299999999999998E-2</v>
+      </c>
+      <c r="W32">
+        <v>4.9149000000000003</v>
+      </c>
+      <c r="X32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="5:24" x14ac:dyDescent="0.25">
+      <c r="E33">
+        <v>1.4109779404</v>
+      </c>
+      <c r="F33">
+        <v>0.2</v>
+      </c>
+      <c r="G33">
+        <v>3.1415999999999999</v>
+      </c>
+      <c r="H33">
+        <v>1.3890525475</v>
+      </c>
+      <c r="I33">
+        <v>0.12</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>0.24685834309999999</v>
+      </c>
+      <c r="L33">
+        <v>4.5298125568999996</v>
+      </c>
+      <c r="M33">
+        <v>2.6684535819000001</v>
+      </c>
+      <c r="N33" t="s">
+        <v>44</v>
+      </c>
+      <c r="R33">
+        <v>1.35</v>
+      </c>
+      <c r="S33">
+        <v>0.2</v>
+      </c>
+      <c r="T33">
+        <v>3.1419999999999999</v>
+      </c>
+      <c r="U33">
+        <v>1.3283</v>
+      </c>
+      <c r="V33">
+        <v>0.1167</v>
+      </c>
+      <c r="W33">
+        <v>0</v>
+      </c>
+      <c r="X33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="5:24" x14ac:dyDescent="0.25">
+      <c r="E34">
+        <v>1.4747736548999999</v>
+      </c>
+      <c r="F34">
+        <v>0.2</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>1.4750904852</v>
+      </c>
+      <c r="I34">
+        <v>0.12</v>
+      </c>
+      <c r="J34">
+        <v>3.1415999999999999</v>
+      </c>
+      <c r="K34">
+        <v>2.1243312033000001</v>
+      </c>
+      <c r="L34">
+        <v>0.98146476360000001</v>
+      </c>
+      <c r="M34">
+        <v>2.2301814902000001</v>
+      </c>
+      <c r="N34" t="s">
+        <v>44</v>
+      </c>
+      <c r="R34">
+        <v>1.4725999999999999</v>
+      </c>
+      <c r="S34">
+        <v>0.2</v>
+      </c>
+      <c r="T34">
+        <v>0</v>
+      </c>
+      <c r="U34">
+        <v>1.4729000000000001</v>
+      </c>
+      <c r="V34">
+        <v>0.11990000000000001</v>
+      </c>
+      <c r="W34">
+        <v>3.1415999999999999</v>
+      </c>
+      <c r="X34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="5:24" x14ac:dyDescent="0.25">
+      <c r="E35">
+        <v>1.1341222659000001</v>
+      </c>
+      <c r="F35">
+        <v>0.12</v>
+      </c>
+      <c r="G35">
+        <v>0.78539999999999999</v>
+      </c>
+      <c r="H35">
+        <v>1.3710979794</v>
+      </c>
+      <c r="I35">
+        <v>0.04</v>
+      </c>
+      <c r="J35">
+        <v>1.5708</v>
+      </c>
+      <c r="K35">
+        <v>3.8924485742999999</v>
+      </c>
+      <c r="L35">
+        <v>4.3783496642999999</v>
+      </c>
+      <c r="M35">
+        <v>1.6360280112000001</v>
+      </c>
+      <c r="N35" t="s">
+        <v>44</v>
+      </c>
+      <c r="R35">
+        <v>1.21</v>
+      </c>
+      <c r="S35">
+        <v>0.1183</v>
+      </c>
+      <c r="T35">
+        <v>0.82889999999999997</v>
+      </c>
+      <c r="U35">
+        <v>1.2825</v>
+      </c>
+      <c r="V35">
+        <v>3.5499999999999997E-2</v>
+      </c>
+      <c r="W35">
+        <v>1.5827</v>
+      </c>
+      <c r="X35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="5:24" x14ac:dyDescent="0.25">
+      <c r="E36">
+        <v>0.785852255</v>
+      </c>
+      <c r="F36">
+        <v>0.1</v>
+      </c>
+      <c r="G36">
+        <v>0.78539999999999999</v>
+      </c>
+      <c r="H36">
+        <v>0.39355619479999998</v>
+      </c>
+      <c r="I36">
+        <v>0.02</v>
+      </c>
+      <c r="J36">
+        <v>5.4977999999999998</v>
+      </c>
+      <c r="K36">
+        <v>4.5109081914000004</v>
+      </c>
+      <c r="L36">
+        <v>2.9663132843</v>
+      </c>
+      <c r="M36">
+        <v>3.8683553511</v>
+      </c>
+      <c r="N36" t="s">
+        <v>44</v>
+      </c>
+      <c r="R36">
+        <v>0.38240000000000002</v>
+      </c>
+      <c r="S36">
+        <v>0.18099999999999999</v>
+      </c>
+      <c r="T36">
+        <v>0.81110000000000004</v>
+      </c>
+      <c r="U36">
+        <v>0.57420000000000004</v>
+      </c>
+      <c r="V36">
+        <v>2.41E-2</v>
+      </c>
+      <c r="W36">
+        <v>5.8999999999999999E-3</v>
+      </c>
+      <c r="X36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="5:24" x14ac:dyDescent="0.25">
+      <c r="E37">
+        <v>0.4787670047</v>
+      </c>
+      <c r="F37">
+        <v>0.2</v>
+      </c>
+      <c r="G37">
+        <v>4.7123999999999997</v>
+      </c>
+      <c r="H37">
+        <v>0.35541469809999998</v>
+      </c>
+      <c r="I37">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="J37">
+        <v>3.1415999999999999</v>
+      </c>
+      <c r="K37">
+        <v>4.9350065225000002</v>
+      </c>
+      <c r="L37">
+        <v>4.6708884390999996</v>
+      </c>
+      <c r="M37">
+        <v>0.64099500450000002</v>
+      </c>
+      <c r="N37" t="s">
+        <v>44</v>
+      </c>
+      <c r="R37">
+        <v>0.71199999999999997</v>
+      </c>
+      <c r="S37">
+        <v>0.17519999999999999</v>
+      </c>
+      <c r="T37">
+        <v>4.6016000000000004</v>
+      </c>
+      <c r="U37">
+        <v>0.35980000000000001</v>
+      </c>
+      <c r="V37">
+        <v>0.13020000000000001</v>
+      </c>
+      <c r="W37">
+        <v>2.4489000000000001</v>
+      </c>
+      <c r="X37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="5:24" x14ac:dyDescent="0.25">
+      <c r="E38">
+        <v>1.2825258852999999</v>
+      </c>
+      <c r="F38">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="G38">
+        <v>2.3561999999999999</v>
+      </c>
+      <c r="H38">
+        <v>1.1085226837</v>
+      </c>
+      <c r="I38">
+        <v>0.08</v>
+      </c>
+      <c r="J38">
+        <v>3.1415999999999999</v>
+      </c>
+      <c r="K38">
+        <v>5.0541583899999999E-2</v>
+      </c>
+      <c r="L38">
+        <v>4.9578693537999996</v>
+      </c>
+      <c r="M38">
+        <v>3.9886280456000001</v>
+      </c>
+      <c r="N38" t="s">
+        <v>44</v>
+      </c>
+      <c r="R38">
+        <v>1.1608000000000001</v>
+      </c>
+      <c r="S38">
+        <v>0.1416</v>
+      </c>
+      <c r="T38">
+        <v>2.2812999999999999</v>
+      </c>
+      <c r="U38">
+        <v>1.2569999999999999</v>
+      </c>
+      <c r="V38">
+        <v>8.5900000000000004E-2</v>
+      </c>
+      <c r="W38">
+        <v>3.1202999999999999</v>
+      </c>
+      <c r="X38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="5:24" x14ac:dyDescent="0.25">
+      <c r="E39">
+        <v>1.0319949839</v>
+      </c>
+      <c r="F39">
+        <v>0.18</v>
+      </c>
+      <c r="G39">
+        <v>3.927</v>
+      </c>
+      <c r="H39">
+        <v>1.1733448184999999</v>
+      </c>
+      <c r="I39">
+        <v>0.12</v>
+      </c>
+      <c r="J39">
+        <v>0.78539999999999999</v>
+      </c>
+      <c r="K39">
+        <v>4.3201662060999997</v>
+      </c>
+      <c r="L39">
+        <v>3.8378352410000001</v>
+      </c>
+      <c r="M39">
+        <v>4.8360302252</v>
+      </c>
+      <c r="N39" t="s">
+        <v>44</v>
+      </c>
+      <c r="R39">
+        <v>0.84179999999999999</v>
+      </c>
+      <c r="S39">
+        <v>0.18970000000000001</v>
+      </c>
+      <c r="T39">
+        <v>3.927</v>
+      </c>
+      <c r="U39">
+        <v>0.9839</v>
+      </c>
+      <c r="V39">
+        <v>0.1163</v>
+      </c>
+      <c r="W39">
+        <v>0.78549999999999998</v>
+      </c>
+      <c r="X39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="5:24" x14ac:dyDescent="0.25">
+      <c r="E40">
+        <v>0.54659396309999997</v>
+      </c>
+      <c r="F40">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="G40">
+        <v>3.927</v>
+      </c>
+      <c r="H40">
+        <v>0.37475583969999998</v>
+      </c>
+      <c r="I40">
+        <v>0.08</v>
+      </c>
+      <c r="J40">
+        <v>1.5708</v>
+      </c>
+      <c r="K40">
+        <v>1.2326114607000001</v>
+      </c>
+      <c r="L40">
+        <v>3.5091223980000001</v>
+      </c>
+      <c r="M40">
+        <v>2.8278096824999999</v>
+      </c>
+      <c r="N40" t="s">
+        <v>44</v>
+      </c>
+      <c r="R40">
+        <v>0.45279999999999998</v>
+      </c>
+      <c r="S40">
+        <v>0.15090000000000001</v>
+      </c>
+      <c r="T40">
+        <v>3.8860999999999999</v>
+      </c>
+      <c r="U40">
+        <v>0.3</v>
+      </c>
+      <c r="V40">
+        <v>7.4899999999999994E-2</v>
+      </c>
+      <c r="W40">
+        <v>1.7507999999999999</v>
+      </c>
+      <c r="X40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="5:24" x14ac:dyDescent="0.25">
+      <c r="E41">
+        <v>0.62359206519999999</v>
+      </c>
+      <c r="F41">
+        <v>0.08</v>
+      </c>
+      <c r="G41">
+        <v>5.4977999999999998</v>
+      </c>
+      <c r="H41">
+        <v>0.47877904049999997</v>
+      </c>
+      <c r="I41">
+        <v>0.02</v>
+      </c>
+      <c r="J41">
+        <v>3.927</v>
+      </c>
+      <c r="K41">
+        <v>2.2205178402999999</v>
+      </c>
+      <c r="L41">
+        <v>1.9827336431</v>
+      </c>
+      <c r="M41">
+        <v>0.36676452050000002</v>
+      </c>
+      <c r="N41" t="s">
+        <v>44</v>
+      </c>
+      <c r="R41">
+        <v>0.97070000000000001</v>
+      </c>
+      <c r="S41">
+        <v>5.8400000000000001E-2</v>
+      </c>
+      <c r="T41">
+        <v>5.508</v>
+      </c>
+      <c r="U41">
+        <v>0.59930000000000005</v>
+      </c>
+      <c r="V41">
+        <v>2.0799999999999999E-2</v>
+      </c>
+      <c r="W41">
+        <v>3.3094999999999999</v>
+      </c>
+      <c r="X41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="5:24" x14ac:dyDescent="0.25">
+      <c r="E42">
+        <v>1.3484992293</v>
+      </c>
+      <c r="F42">
+        <v>0.2</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>0.39122828500000001</v>
+      </c>
+      <c r="I42">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="J42">
+        <v>0.78539999999999999</v>
+      </c>
+      <c r="K42">
+        <v>1.9402253723</v>
+      </c>
+      <c r="L42">
+        <v>1.6478522000000001E-3</v>
+      </c>
+      <c r="M42">
+        <v>3.2221664534999999</v>
+      </c>
+      <c r="N42" t="s">
+        <v>44</v>
+      </c>
+      <c r="R42">
+        <v>1.3119000000000001</v>
+      </c>
+      <c r="S42">
+        <v>0.19980000000000001</v>
+      </c>
+      <c r="T42">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="U42">
+        <v>0.41370000000000001</v>
+      </c>
+      <c r="V42">
+        <v>0.14530000000000001</v>
+      </c>
+      <c r="W42">
+        <v>0.70740000000000003</v>
+      </c>
+      <c r="X42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="5:24" x14ac:dyDescent="0.25">
+      <c r="E43">
+        <v>0.51681038229999998</v>
+      </c>
+      <c r="F43">
+        <v>0.08</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>0.91461204240000005</v>
+      </c>
+      <c r="I43">
+        <v>0.02</v>
+      </c>
+      <c r="J43">
+        <v>3.927</v>
+      </c>
+      <c r="K43">
+        <v>3.7945339589999998</v>
+      </c>
+      <c r="L43">
+        <v>3.3481721828</v>
+      </c>
+      <c r="M43">
+        <v>3.4429632493</v>
+      </c>
+      <c r="N43" t="s">
+        <v>44</v>
+      </c>
+      <c r="R43">
+        <v>0.5534</v>
+      </c>
+      <c r="S43">
+        <v>0.1079</v>
+      </c>
+      <c r="T43">
+        <v>0.39450000000000002</v>
+      </c>
+      <c r="U43">
+        <v>1.0716000000000001</v>
+      </c>
+      <c r="V43">
+        <v>4.1799999999999997E-2</v>
+      </c>
+      <c r="W43">
+        <v>4.0719000000000003</v>
+      </c>
+      <c r="X43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="5:24" x14ac:dyDescent="0.25">
+      <c r="E44">
+        <v>0.68441694529999997</v>
+      </c>
+      <c r="F44">
+        <v>0.16</v>
+      </c>
+      <c r="G44">
+        <v>2.3561999999999999</v>
+      </c>
+      <c r="H44">
+        <v>1.4072090791</v>
+      </c>
+      <c r="I44">
+        <v>0.1</v>
+      </c>
+      <c r="J44">
+        <v>0.78539999999999999</v>
+      </c>
+      <c r="K44">
+        <v>1.6472032243000001</v>
+      </c>
+      <c r="L44">
+        <v>5.9795420000000002E-2</v>
+      </c>
+      <c r="M44">
+        <v>0.1036992028</v>
+      </c>
+      <c r="N44" t="s">
+        <v>44</v>
+      </c>
+      <c r="R44">
+        <v>0.8014</v>
+      </c>
+      <c r="S44">
+        <v>0.1618</v>
+      </c>
+      <c r="T44">
+        <v>1.7798</v>
+      </c>
+      <c r="U44">
+        <v>0.97699999999999998</v>
+      </c>
+      <c r="V44">
+        <v>7.2900000000000006E-2</v>
+      </c>
+      <c r="W44">
+        <v>0.80459999999999998</v>
+      </c>
+      <c r="X44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="5:24" x14ac:dyDescent="0.25">
+      <c r="E45">
+        <v>1.3991334753</v>
+      </c>
+      <c r="F45">
+        <v>0.12</v>
+      </c>
+      <c r="G45">
+        <v>5.4977999999999998</v>
+      </c>
+      <c r="H45">
+        <v>0.96266422490000003</v>
+      </c>
+      <c r="I45">
+        <v>0.06</v>
+      </c>
+      <c r="J45">
+        <v>5.4977999999999998</v>
+      </c>
+      <c r="K45">
+        <v>2.0231526378</v>
+      </c>
+      <c r="L45">
+        <v>0.50988481399999996</v>
+      </c>
+      <c r="M45">
+        <v>0.60427768879999999</v>
+      </c>
+      <c r="N45" t="s">
+        <v>44</v>
+      </c>
+      <c r="R45">
+        <v>1.5</v>
+      </c>
+      <c r="S45">
+        <v>0.1071</v>
+      </c>
+      <c r="T45">
+        <v>4.8140999999999998</v>
+      </c>
+      <c r="U45">
+        <v>1.5</v>
+      </c>
+      <c r="V45">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="W45">
+        <v>0</v>
+      </c>
+      <c r="X45">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="46" spans="5:24" x14ac:dyDescent="0.25">
+      <c r="E46">
+        <v>0.4668308846</v>
+      </c>
+      <c r="F46">
+        <v>0.08</v>
+      </c>
+      <c r="G46">
+        <v>3.1415999999999999</v>
+      </c>
+      <c r="H46">
+        <v>1.1054712231999999</v>
+      </c>
+      <c r="I46">
+        <v>0.04</v>
+      </c>
+      <c r="J46">
+        <v>4.7123999999999997</v>
+      </c>
+      <c r="K46">
+        <v>4.4838346888</v>
+      </c>
+      <c r="L46">
+        <v>0.20145099390000001</v>
+      </c>
+      <c r="M46">
+        <v>4.5041045776999997</v>
+      </c>
+      <c r="N46" t="s">
+        <v>44</v>
+      </c>
+      <c r="R46">
+        <v>0.59330000000000005</v>
+      </c>
+      <c r="S46">
+        <v>7.6600000000000001E-2</v>
+      </c>
+      <c r="T46">
+        <v>3.7166999999999999</v>
+      </c>
+      <c r="U46">
+        <v>0.78310000000000002</v>
+      </c>
+      <c r="V46">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="W46">
+        <v>4.7519</v>
+      </c>
+      <c r="X46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="5:24" x14ac:dyDescent="0.25">
+      <c r="E47">
+        <v>1.4827422800000001</v>
+      </c>
+      <c r="F47">
+        <v>0.08</v>
+      </c>
+      <c r="G47">
+        <v>3.1415999999999999</v>
+      </c>
+      <c r="H47">
+        <v>0.80651000630000003</v>
+      </c>
+      <c r="I47">
+        <v>0.04</v>
+      </c>
+      <c r="J47">
+        <v>4.7123999999999997</v>
+      </c>
+      <c r="K47">
+        <v>4.1839238480000001</v>
+      </c>
+      <c r="L47">
+        <v>4.1752821560999998</v>
+      </c>
+      <c r="M47">
+        <v>0.4978333036</v>
+      </c>
+      <c r="N47" t="s">
+        <v>44</v>
+      </c>
+      <c r="R47">
+        <v>1.1761999999999999</v>
+      </c>
+      <c r="S47">
+        <v>8.7800000000000003E-2</v>
+      </c>
+      <c r="T47">
+        <v>2.9220000000000002</v>
+      </c>
+      <c r="U47">
+        <v>1.1135999999999999</v>
+      </c>
+      <c r="V47">
+        <v>5.1400000000000001E-2</v>
+      </c>
+      <c r="W47">
+        <v>4.4063999999999997</v>
+      </c>
+      <c r="X47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="5:24" x14ac:dyDescent="0.25">
+      <c r="E48">
+        <v>1.4313963908</v>
+      </c>
+      <c r="F48">
+        <v>0.2</v>
+      </c>
+      <c r="G48">
+        <v>5.4977999999999998</v>
+      </c>
+      <c r="H48">
+        <v>0.66088478610000001</v>
+      </c>
+      <c r="I48">
+        <v>0.16</v>
+      </c>
+      <c r="J48">
+        <v>5.4977999999999998</v>
+      </c>
+      <c r="K48">
+        <v>4.6493399877000003</v>
+      </c>
+      <c r="L48">
+        <v>1.9654430356000001</v>
+      </c>
+      <c r="M48">
+        <v>1.6399488998</v>
+      </c>
+      <c r="N48" t="s">
+        <v>44</v>
+      </c>
+      <c r="R48">
+        <v>1.4564999999999999</v>
+      </c>
+      <c r="S48">
+        <v>0.18559999999999999</v>
+      </c>
+      <c r="T48">
+        <v>6.1999999999999998E-3</v>
+      </c>
+      <c r="U48">
+        <v>1.4892000000000001</v>
+      </c>
+      <c r="V48">
+        <v>0.18559999999999999</v>
+      </c>
+      <c r="W48">
+        <v>4.7282000000000002</v>
+      </c>
+      <c r="X48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="5:24" x14ac:dyDescent="0.25">
+      <c r="E49">
+        <v>1.1008731407000001</v>
+      </c>
+      <c r="F49">
+        <v>0.12</v>
+      </c>
+      <c r="G49">
+        <v>4.7123999999999997</v>
+      </c>
+      <c r="H49">
+        <v>1.0118865585000001</v>
+      </c>
+      <c r="I49">
+        <v>0.08</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>2.5804466663999999</v>
+      </c>
+      <c r="L49">
+        <v>2.8020908323999998</v>
+      </c>
+      <c r="M49">
+        <v>1.4209598912000001</v>
+      </c>
+      <c r="N49" t="s">
+        <v>44</v>
+      </c>
+      <c r="R49">
+        <v>1.2199</v>
+      </c>
+      <c r="S49">
+        <v>0.1169</v>
+      </c>
+      <c r="T49">
+        <v>5.0364000000000004</v>
+      </c>
+      <c r="U49">
+        <v>0.62649999999999995</v>
+      </c>
+      <c r="V49">
+        <v>5.6300000000000003E-2</v>
+      </c>
+      <c r="W49">
+        <v>8.9800000000000005E-2</v>
+      </c>
+      <c r="X49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="5:24" x14ac:dyDescent="0.25">
+      <c r="E50">
+        <v>1.1548404238000001</v>
+      </c>
+      <c r="F50">
+        <v>0.06</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>0.95560731600000004</v>
+      </c>
+      <c r="I50">
+        <v>0.02</v>
+      </c>
+      <c r="J50">
+        <v>5.4977999999999998</v>
+      </c>
+      <c r="K50">
+        <v>1.7445767312</v>
+      </c>
+      <c r="L50">
+        <v>3.9458122761999999</v>
+      </c>
+      <c r="M50">
+        <v>4.9189190299999996</v>
+      </c>
+      <c r="N50" t="s">
+        <v>44</v>
+      </c>
+      <c r="R50">
+        <v>1.3264</v>
+      </c>
+      <c r="S50">
+        <v>5.3600000000000002E-2</v>
+      </c>
+      <c r="T50">
+        <v>0</v>
+      </c>
+      <c r="U50">
+        <v>0.50419999999999998</v>
+      </c>
+      <c r="V50">
+        <v>2.3E-2</v>
+      </c>
+      <c r="W50">
+        <v>0</v>
+      </c>
+      <c r="X50">
+        <v>1.2999999999999999E-3</v>
+      </c>
+    </row>
+    <row r="51" spans="5:24" x14ac:dyDescent="0.25">
+      <c r="E51">
+        <v>1.1816252039999999</v>
+      </c>
+      <c r="F51">
+        <v>0.08</v>
+      </c>
+      <c r="G51">
+        <v>1.5708</v>
+      </c>
+      <c r="H51">
+        <v>0.57227119820000005</v>
+      </c>
+      <c r="I51">
+        <v>0.04</v>
+      </c>
+      <c r="J51">
+        <v>0.78539999999999999</v>
+      </c>
+      <c r="K51">
+        <v>1.4076592733</v>
+      </c>
+      <c r="L51">
+        <v>1.3192874408999999</v>
+      </c>
+      <c r="M51">
+        <v>2.6835966308999999</v>
+      </c>
+      <c r="N51" t="s">
+        <v>44</v>
+      </c>
+      <c r="R51">
+        <v>0.79210000000000003</v>
+      </c>
+      <c r="S51">
+        <v>9.4600000000000004E-2</v>
+      </c>
+      <c r="T51">
+        <v>1.6161000000000001</v>
+      </c>
+      <c r="U51">
+        <v>0.90890000000000004</v>
+      </c>
+      <c r="V51">
+        <v>4.4499999999999998E-2</v>
+      </c>
+      <c r="W51">
+        <v>1.0648</v>
+      </c>
+      <c r="X51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="5:24" x14ac:dyDescent="0.25">
+      <c r="E52">
+        <v>0.93729510640000002</v>
+      </c>
+      <c r="F52">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="G52">
+        <v>0.78539999999999999</v>
+      </c>
+      <c r="H52">
+        <v>0.49250416219999998</v>
+      </c>
+      <c r="I52">
+        <v>0.1</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52">
+        <v>0.50502447429999997</v>
+      </c>
+      <c r="L52">
+        <v>3.7817597896000001</v>
+      </c>
+      <c r="M52">
+        <v>0.94479070089999995</v>
+      </c>
+      <c r="N52" t="s">
+        <v>45</v>
+      </c>
+      <c r="R52">
+        <v>0.79090000000000005</v>
+      </c>
+      <c r="S52">
+        <v>0.1434</v>
+      </c>
+      <c r="T52">
+        <v>0.85640000000000005</v>
+      </c>
+      <c r="U52">
+        <v>0.63990000000000002</v>
+      </c>
+      <c r="V52">
+        <v>0.1066</v>
+      </c>
+      <c r="W52">
+        <v>0.1045</v>
+      </c>
+      <c r="X52">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -27257,7 +30455,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E12580AD17ADB64691A1BA4C2E042DA4" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="6532fc6a52f3455fe895a4f720bca71c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8" xmlns:ns4="08a9f8ec-165a-4165-a8e9-ed45c2de7bcb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d9a2f75daf18a7097de825f86ff3fec6" ns3:_="" ns4:_="">
     <xsd:import namespace="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8"/>
@@ -27510,15 +30708,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE208467-E14A-4CB9-9FC8-72DFB8E94FF2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="08a9f8ec-165a-4165-a8e9-ed45c2de7bcb"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D595912-0053-4104-933F-CDA3B3DBC546}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -27526,7 +30733,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65923CC5-95C4-4597-AADE-A0DCE38786F0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -27543,21 +30750,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE208467-E14A-4CB9-9FC8-72DFB8E94FF2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="08a9f8ec-165a-4165-a8e9-ed45c2de7bcb"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>